--- a/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2059.29</v>
+        <v>28712.43</v>
       </c>
       <c r="C4" t="n">
-        <v>593208</v>
+        <v>5139792</v>
       </c>
       <c r="D4" t="n">
-        <v>466092</v>
+        <v>4038408</v>
       </c>
       <c r="E4" t="n">
-        <v>149400</v>
+        <v>1575000</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>6660</v>
+        <v>83940</v>
       </c>
       <c r="H4" t="n">
-        <v>300</v>
+        <v>7140</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20790</v>
+        <v>172020</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3705.3</v>
+        <v>24105.96</v>
       </c>
       <c r="C5" t="n">
-        <v>666792</v>
+        <v>4262328</v>
       </c>
       <c r="D5" t="n">
-        <v>523908</v>
+        <v>3348972</v>
       </c>
       <c r="E5" t="n">
-        <v>132300</v>
+        <v>1046700</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>8520</v>
+        <v>68310</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>6270</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20520</v>
+        <v>164670</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4066.74</v>
+        <v>24991.29</v>
       </c>
       <c r="C6" t="n">
-        <v>487872</v>
+        <v>3873744</v>
       </c>
       <c r="D6" t="n">
-        <v>383328</v>
+        <v>3043656</v>
       </c>
       <c r="E6" t="n">
-        <v>77400</v>
+        <v>879300</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>8160</v>
+        <v>70200</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7710</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>22800</v>
+        <v>158550</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3013.74</v>
+        <v>33500.79</v>
       </c>
       <c r="C7" t="n">
-        <v>265104</v>
+        <v>4555656</v>
       </c>
       <c r="D7" t="n">
-        <v>208296</v>
+        <v>3579444</v>
       </c>
       <c r="E7" t="n">
-        <v>39600</v>
+        <v>786600</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>86490</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11730</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>5460</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13440</v>
+        <v>202890</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1588.32</v>
+        <v>27725.31</v>
       </c>
       <c r="C8" t="n">
-        <v>90720</v>
+        <v>2275056</v>
       </c>
       <c r="D8" t="n">
-        <v>71280</v>
+        <v>1787544</v>
       </c>
       <c r="E8" t="n">
-        <v>19800</v>
+        <v>247500</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2370</v>
+        <v>58710</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4770</v>
+        <v>124650</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>753.66</v>
+        <v>23419.62</v>
       </c>
       <c r="C9" t="n">
-        <v>38304</v>
+        <v>1676304</v>
       </c>
       <c r="D9" t="n">
-        <v>30096</v>
+        <v>1317096</v>
       </c>
       <c r="E9" t="n">
-        <v>9000</v>
+        <v>133200</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>36210</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>960</v>
+        <v>73080</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>426.06</v>
+        <v>12549.87</v>
       </c>
       <c r="C10" t="n">
-        <v>4536</v>
+        <v>840168</v>
       </c>
       <c r="D10" t="n">
-        <v>3564</v>
+        <v>660132</v>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>45900</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>630</v>
+        <v>19440</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10095,13 +10089,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>630</v>
+        <v>38430</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>275.49</v>
+        <v>1375.02</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>106848</v>
       </c>
       <c r="D11" t="n">
-        <v>1188</v>
+        <v>83952</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>2520</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>9450</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>161.01</v>
+        <v>284.76</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>30744</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>24156</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>134.01</v>
+        <v>179.55</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>8568</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>6732</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>125.19</v>
+        <v>96.84</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>840</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>12.24</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.17</v>
+        <v>17.64</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>10.26</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>4.77</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>1.44</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20">
@@ -10451,13 +10445,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -10492,10 +10486,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1667.39</v>
+        <v>10847.68</v>
       </c>
       <c r="C5" t="n">
-        <v>366735.6</v>
+        <v>2344280.4</v>
       </c>
       <c r="D5" t="n">
-        <v>173413.55</v>
+        <v>1108509.73</v>
       </c>
       <c r="E5" t="n">
-        <v>14592.69</v>
+        <v>115451.01</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10.8</v>
+        <v>2257.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4309.2</v>
+        <v>34580.7</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3253.39</v>
+        <v>19993.03</v>
       </c>
       <c r="C6" t="n">
-        <v>439084.8</v>
+        <v>3486369.6</v>
       </c>
       <c r="D6" t="n">
-        <v>194347.3</v>
+        <v>1543133.59</v>
       </c>
       <c r="E6" t="n">
-        <v>13080.6</v>
+        <v>148601.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>408</v>
+        <v>3510</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4394.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8436</v>
+        <v>58663.5</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2863.05</v>
+        <v>31825.75</v>
       </c>
       <c r="C7" t="n">
-        <v>265104</v>
+        <v>4555656</v>
       </c>
       <c r="D7" t="n">
-        <v>132892.85</v>
+        <v>2283685.27</v>
       </c>
       <c r="E7" t="n">
-        <v>8422.92</v>
+        <v>167309.82</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>819</v>
+        <v>12973.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8562.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8064</v>
+        <v>121734</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1588.32</v>
+        <v>27725.31</v>
       </c>
       <c r="C8" t="n">
-        <v>90720</v>
+        <v>2275056</v>
       </c>
       <c r="D8" t="n">
-        <v>52462.08</v>
+        <v>1315632.38</v>
       </c>
       <c r="E8" t="n">
-        <v>4856.94</v>
+        <v>60711.75</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1540.5</v>
+        <v>38161.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2218.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3386.7</v>
+        <v>88501.5</v>
       </c>
     </row>
     <row r="9">
@@ -11897,37 +11891,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>753.66</v>
+        <v>23419.62</v>
       </c>
       <c r="C9" t="n">
-        <v>38304</v>
+        <v>1676304</v>
       </c>
       <c r="D9" t="n">
-        <v>24167.09</v>
+        <v>1057628.09</v>
       </c>
       <c r="E9" t="n">
-        <v>2409.3</v>
+        <v>35657.64</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>841.5</v>
+        <v>30778.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>777.6</v>
+        <v>59194.8</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>426.06</v>
+        <v>12549.87</v>
       </c>
       <c r="C10" t="n">
-        <v>4536</v>
+        <v>840168</v>
       </c>
       <c r="D10" t="n">
-        <v>3100.68</v>
+        <v>574314.84</v>
       </c>
       <c r="E10" t="n">
-        <v>522</v>
+        <v>13311</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>630</v>
+        <v>19440</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11959,13 +11953,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>560.7</v>
+        <v>34202.7</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>275.49</v>
+        <v>1375.02</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>106848</v>
       </c>
       <c r="D11" t="n">
-        <v>1067.42</v>
+        <v>75430.87</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1475.28</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>2520</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>9450</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>161.01</v>
+        <v>284.76</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>30744</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>22392.61</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>860.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>134.01</v>
+        <v>179.55</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>8568</v>
       </c>
       <c r="D13" t="n">
-        <v>376</v>
+        <v>6392.03</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>125.19</v>
+        <v>96.84</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1154.74</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>840</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>12.24</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2733.19</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.17</v>
+        <v>17.64</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>10.26</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>4.77</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>1.44</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20">
@@ -12315,13 +12309,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12330,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -12356,10 +12350,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3668247</v>
+        <v>23864900.4</v>
       </c>
       <c r="C5" t="n">
-        <v>20170458</v>
+        <v>128935422</v>
       </c>
       <c r="D5" t="n">
-        <v>17571994.82</v>
+        <v>112325291.14</v>
       </c>
       <c r="E5" t="n">
-        <v>2688557.21</v>
+        <v>21270694.08</v>
       </c>
       <c r="F5" t="n">
-        <v>2500.02</v>
+        <v>16666.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2987.82</v>
+        <v>624454.38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40592.66</v>
+        <v>325750.19</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7157462.4</v>
+        <v>43984670.4</v>
       </c>
       <c r="C6" t="n">
-        <v>24149664</v>
+        <v>191750328</v>
       </c>
       <c r="D6" t="n">
-        <v>19693211.5</v>
+        <v>156365726.88</v>
       </c>
       <c r="E6" t="n">
-        <v>2409969.74</v>
+        <v>27378377.21</v>
       </c>
       <c r="F6" t="n">
-        <v>29166.9</v>
+        <v>58333.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7548</v>
+        <v>64935</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1215793.75</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>79467.12</v>
+        <v>552610.17</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6298716.6</v>
+        <v>70016651.09999999</v>
       </c>
       <c r="C7" t="n">
-        <v>14580720</v>
+        <v>250561080</v>
       </c>
       <c r="D7" t="n">
-        <v>13466032.29</v>
+        <v>231405828.61</v>
       </c>
       <c r="E7" t="n">
-        <v>1551838.78</v>
+        <v>30825161.24</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>15151.5</v>
+        <v>240009.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2368926.28</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>40833.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>75962.88</v>
+        <v>1146734.28</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3494304</v>
+        <v>60995682</v>
       </c>
       <c r="C8" t="n">
-        <v>4989600</v>
+        <v>125128080</v>
       </c>
       <c r="D8" t="n">
-        <v>5315982.57</v>
+        <v>133313029.47</v>
       </c>
       <c r="E8" t="n">
-        <v>894842.63</v>
+        <v>11185532.82</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>28499.25</v>
+        <v>705987.75</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>613748.02</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>31902.71</v>
+        <v>833684.13</v>
       </c>
     </row>
     <row r="9">
@@ -12829,37 +12823,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1658052</v>
+        <v>51523164</v>
       </c>
       <c r="C9" t="n">
-        <v>2106720</v>
+        <v>92196720</v>
       </c>
       <c r="D9" t="n">
-        <v>2448851.03</v>
+        <v>107169454.16</v>
       </c>
       <c r="E9" t="n">
-        <v>443889.43</v>
+        <v>6569563.59</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>15567.75</v>
+        <v>569402.25</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>74695.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7324.99</v>
+        <v>557615.02</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>937332</v>
+        <v>27609714</v>
       </c>
       <c r="C10" t="n">
-        <v>249480</v>
+        <v>46209240</v>
       </c>
       <c r="D10" t="n">
-        <v>314191.9</v>
+        <v>58195322.74</v>
       </c>
       <c r="E10" t="n">
-        <v>96173.28</v>
+        <v>2452418.64</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11655</v>
+        <v>359640</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,13 +12885,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>58333</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5281.79</v>
+        <v>322189.43</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>606078</v>
+        <v>3025044</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>5876640</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>7643410.26</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>271805.59</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3330</v>
+        <v>46620</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1978.2</v>
+        <v>89019</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>354222</v>
+        <v>626472</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>1690920</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>2269043.37</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>158520.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>17205</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>42107.4</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>294822</v>
+        <v>395010</v>
       </c>
       <c r="C13" t="n">
-        <v>27720</v>
+        <v>471240</v>
       </c>
       <c r="D13" t="n">
-        <v>38100.28</v>
+        <v>647704.8100000001</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>3330</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>27129.6</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>275418</v>
+        <v>213048</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>117009.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>4440</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>7912.8</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>14058</v>
+        <v>26928</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>276954.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2574</v>
+        <v>38808</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2543.4</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>22572</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3673.8</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>3168</v>
+        <v>10494</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>3168</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5369.4</v>
       </c>
     </row>
     <row r="20">
@@ -13247,13 +13241,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>249480</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>361140.12</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>67155</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -13288,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>28712.43</v>
+        <v>35636.31</v>
       </c>
       <c r="C4" t="n">
-        <v>5139792</v>
+        <v>3646440</v>
       </c>
       <c r="D4" t="n">
-        <v>4038408</v>
+        <v>2865060</v>
       </c>
       <c r="E4" t="n">
-        <v>1575000</v>
+        <v>1043100</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>83940</v>
+        <v>107280</v>
       </c>
       <c r="H4" t="n">
-        <v>7140</v>
+        <v>13650</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>172020</v>
+        <v>343140</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24105.96</v>
+        <v>11607.84</v>
       </c>
       <c r="C5" t="n">
-        <v>4262328</v>
+        <v>782712</v>
       </c>
       <c r="D5" t="n">
-        <v>3348972</v>
+        <v>614988</v>
       </c>
       <c r="E5" t="n">
-        <v>1046700</v>
+        <v>241200</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>68310</v>
+        <v>30300</v>
       </c>
       <c r="H5" t="n">
-        <v>6270</v>
+        <v>2910</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>164670</v>
+        <v>110880</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>24991.29</v>
+        <v>1142.46</v>
       </c>
       <c r="C6" t="n">
-        <v>3873744</v>
+        <v>109872</v>
       </c>
       <c r="D6" t="n">
-        <v>3043656</v>
+        <v>86328</v>
       </c>
       <c r="E6" t="n">
-        <v>879300</v>
+        <v>31500</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>70200</v>
+        <v>4110</v>
       </c>
       <c r="H6" t="n">
-        <v>7710</v>
+        <v>330</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>158550</v>
+        <v>18780</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>33500.79</v>
+        <v>150.21</v>
       </c>
       <c r="C7" t="n">
-        <v>4555656</v>
+        <v>26712</v>
       </c>
       <c r="D7" t="n">
-        <v>3579444</v>
+        <v>20988</v>
       </c>
       <c r="E7" t="n">
-        <v>786600</v>
+        <v>3600</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>86490</v>
+        <v>780</v>
       </c>
       <c r="H7" t="n">
-        <v>11730</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>202890</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27725.31</v>
+        <v>12.33</v>
       </c>
       <c r="C8" t="n">
-        <v>2275056</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
-        <v>1787544</v>
+        <v>792</v>
       </c>
       <c r="E8" t="n">
-        <v>247500</v>
+        <v>900</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58710</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
-        <v>2610</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>124650</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -13761,37 +13755,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>23419.62</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1676304</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1317096</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>133200</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>36210</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>73080</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>12549.87</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>840168</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>660132</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>19440</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13823,13 +13817,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>38430</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>1375.02</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>106848</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>83952</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>9450</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>284.76</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>30744</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>24156</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>179.55</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>8568</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6732</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>96.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>12.24</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>10.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,7 +14135,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14179,13 +14173,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14194,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -14220,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10847.68</v>
+        <v>5223.53</v>
       </c>
       <c r="C5" t="n">
-        <v>2344280.4</v>
+        <v>430491.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1108509.73</v>
+        <v>203561.03</v>
       </c>
       <c r="E5" t="n">
-        <v>115451.01</v>
+        <v>26604.36</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2257.2</v>
+        <v>1047.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>34580.7</v>
+        <v>23284.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>19993.03</v>
+        <v>913.97</v>
       </c>
       <c r="C6" t="n">
-        <v>3486369.6</v>
+        <v>98884.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1543133.59</v>
+        <v>43768.3</v>
       </c>
       <c r="E6" t="n">
-        <v>148601.7</v>
+        <v>5323.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3510</v>
+        <v>205.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4394.7</v>
+        <v>188.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>58663.5</v>
+        <v>6948.6</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>31825.75</v>
+        <v>142.7</v>
       </c>
       <c r="C7" t="n">
-        <v>4555656</v>
+        <v>26712</v>
       </c>
       <c r="D7" t="n">
-        <v>2283685.27</v>
+        <v>13390.34</v>
       </c>
       <c r="E7" t="n">
-        <v>167309.82</v>
+        <v>765.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12973.5</v>
+        <v>117</v>
       </c>
       <c r="H7" t="n">
-        <v>8562.9</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>121734</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27725.31</v>
+        <v>12.33</v>
       </c>
       <c r="C8" t="n">
-        <v>2275056</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
-        <v>1315632.38</v>
+        <v>582.91</v>
       </c>
       <c r="E8" t="n">
-        <v>60711.75</v>
+        <v>220.77</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>38161.5</v>
+        <v>175.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2218.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>88501.5</v>
+        <v>340.8</v>
       </c>
     </row>
     <row r="9">
@@ -14693,37 +14687,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>23419.62</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1676304</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1057628.09</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>35657.64</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30778.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>59194.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>12549.87</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>840168</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>574314.84</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13311</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>19440</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14755,13 +14749,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>34202.7</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>1375.02</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>106848</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>75430.87</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1475.28</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>9450</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>284.76</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>30744</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>22392.61</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>860.4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>179.55</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>8568</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6392.03</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>96.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1154.74</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>12.24</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2733.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>10.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,7 +15067,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15111,13 +15105,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15126,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -15152,10 +15146,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>23864900.4</v>
+        <v>11491761.6</v>
       </c>
       <c r="C5" t="n">
-        <v>128935422</v>
+        <v>23677038</v>
       </c>
       <c r="D5" t="n">
-        <v>112325291.14</v>
+        <v>20626838.97</v>
       </c>
       <c r="E5" t="n">
-        <v>21270694.08</v>
+        <v>4901587.29</v>
       </c>
       <c r="F5" t="n">
-        <v>16666.8</v>
+        <v>7500.06</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>624454.38</v>
+        <v>289818.54</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>325750.19</v>
+        <v>219342.82</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>43984670.4</v>
+        <v>2010729.6</v>
       </c>
       <c r="C6" t="n">
-        <v>191750328</v>
+        <v>5438664</v>
       </c>
       <c r="D6" t="n">
-        <v>156365726.88</v>
+        <v>4435041.43</v>
       </c>
       <c r="E6" t="n">
-        <v>27378377.21</v>
+        <v>980801.64</v>
       </c>
       <c r="F6" t="n">
-        <v>58333.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>64935</v>
+        <v>3801.75</v>
       </c>
       <c r="H6" t="n">
-        <v>1215793.75</v>
+        <v>52037.86</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>552610.17</v>
+        <v>65455.81</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>70016651.09999999</v>
+        <v>313938.9</v>
       </c>
       <c r="C7" t="n">
-        <v>250561080</v>
+        <v>1469160</v>
       </c>
       <c r="D7" t="n">
-        <v>231405828.61</v>
+        <v>1356843.56</v>
       </c>
       <c r="E7" t="n">
-        <v>30825161.24</v>
+        <v>141076.25</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>240009.75</v>
+        <v>2164.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2368926.28</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1146734.28</v>
+        <v>16616.88</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>60995682</v>
+        <v>27126</v>
       </c>
       <c r="C8" t="n">
-        <v>125128080</v>
+        <v>55440</v>
       </c>
       <c r="D8" t="n">
-        <v>133313029.47</v>
+        <v>59066.47</v>
       </c>
       <c r="E8" t="n">
-        <v>11185532.82</v>
+        <v>40674.66</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>705987.75</v>
+        <v>3246.75</v>
       </c>
       <c r="H8" t="n">
-        <v>613748.02</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>833684.13</v>
+        <v>3210.34</v>
       </c>
     </row>
     <row r="9">
@@ -15625,37 +15619,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>51523164</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>92196720</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>107169454.16</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6569563.59</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>569402.25</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>74695.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>557615.02</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>27609714</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>46209240</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>58195322.74</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2452418.64</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>359640</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15687,13 +15681,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>322189.43</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>3025044</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5876640</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>7643410.26</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>271805.59</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>46620</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>89019</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>626472</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1690920</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2269043.37</v>
-      </c>
-      <c r="E12" t="n">
-        <v>158520.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>17205</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>42107.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>395010</v>
-      </c>
-      <c r="C13" t="n">
-        <v>471240</v>
-      </c>
-      <c r="D13" t="n">
-        <v>647704.8100000001</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>27129.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>213048</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7912.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>26928</v>
-      </c>
-      <c r="C15" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D15" t="n">
-        <v>276954.35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>38808</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2543.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>22572</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3673.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>10494</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3168</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5369.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>198</v>
-      </c>
-      <c r="C20" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D20" t="n">
-        <v>361140.12</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>67155</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3762.45</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1104264</v>
-      </c>
-      <c r="D4" t="n">
-        <v>867636</v>
-      </c>
-      <c r="E4" t="n">
-        <v>361800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13350</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3360</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>34800</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4832.91</v>
-      </c>
-      <c r="C5" t="n">
-        <v>928368</v>
-      </c>
-      <c r="D5" t="n">
-        <v>729432</v>
-      </c>
-      <c r="E5" t="n">
-        <v>216900</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16170</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>35340</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4413.15</v>
-      </c>
-      <c r="C6" t="n">
-        <v>536760</v>
-      </c>
-      <c r="D6" t="n">
-        <v>421740</v>
-      </c>
-      <c r="E6" t="n">
-        <v>105300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11700</v>
-      </c>
-      <c r="H6" t="n">
-        <v>930</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22620</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3999.78</v>
-      </c>
-      <c r="C7" t="n">
-        <v>347760</v>
-      </c>
-      <c r="D7" t="n">
-        <v>273240</v>
-      </c>
-      <c r="E7" t="n">
-        <v>69300</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5040</v>
-      </c>
-      <c r="H7" t="n">
-        <v>390</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14910</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4269.24</v>
-      </c>
-      <c r="C8" t="n">
-        <v>234360</v>
-      </c>
-      <c r="D8" t="n">
-        <v>184140</v>
-      </c>
-      <c r="E8" t="n">
-        <v>39600</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3030</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10590</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4119.75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>204624</v>
-      </c>
-      <c r="D9" t="n">
-        <v>160776</v>
-      </c>
-      <c r="E9" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4290</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>12090</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2751.84</v>
-      </c>
-      <c r="C10" t="n">
-        <v>93240</v>
-      </c>
-      <c r="D10" t="n">
-        <v>73260</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2790</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1944.45</v>
-      </c>
-      <c r="C11" t="n">
-        <v>35280</v>
-      </c>
-      <c r="D11" t="n">
-        <v>27720</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>450</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1069.11</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8568</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6732</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>649.53</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4536</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3564</v>
-      </c>
-      <c r="E13" t="n">
-        <v>900</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>448.38</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>296.1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>347.22</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>356.58</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>131.94</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2174.81</v>
-      </c>
-      <c r="C5" t="n">
-        <v>510602.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>241441.99</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23924.07</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7421.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3530.52</v>
-      </c>
-      <c r="C6" t="n">
-        <v>483084</v>
-      </c>
-      <c r="D6" t="n">
-        <v>213822.18</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17795.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>585</v>
-      </c>
-      <c r="H6" t="n">
-        <v>530.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8369.4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3799.79</v>
-      </c>
-      <c r="C7" t="n">
-        <v>347760</v>
-      </c>
-      <c r="D7" t="n">
-        <v>174327.12</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14740.11</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>756</v>
-      </c>
-      <c r="H7" t="n">
-        <v>284.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8946</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4269.24</v>
-      </c>
-      <c r="C8" t="n">
-        <v>234360</v>
-      </c>
-      <c r="D8" t="n">
-        <v>135527.04</v>
-      </c>
-      <c r="E8" t="n">
-        <v>9713.879999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1969.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7518.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4119.75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>204624</v>
-      </c>
-      <c r="D9" t="n">
-        <v>129103.13</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7227.9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3646.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9792.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2751.84</v>
-      </c>
-      <c r="C10" t="n">
-        <v>93240</v>
-      </c>
-      <c r="D10" t="n">
-        <v>63736.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1566</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2790</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5073</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1944.45</v>
-      </c>
-      <c r="C11" t="n">
-        <v>35280</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24906.42</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>450</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1069.11</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8568</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6240.56</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>649.53</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4536</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3384.02</v>
-      </c>
-      <c r="E13" t="n">
-        <v>476.28</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>448.38</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1924.56</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>296.1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1561.82</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>347.22</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>356.58</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>131.94</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4784580.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>28083132</v>
-      </c>
-      <c r="D5" t="n">
-        <v>24465317.05</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4407770.66</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6666.72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>298782</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>69909.59</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7767144</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26569620</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21666601.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3278679.77</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10822.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>146652.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>78839.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8359540.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>19126800</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17664567.07</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2715717.87</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13986</v>
-      </c>
-      <c r="H7" t="n">
-        <v>78762.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>84271.32000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9392328</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12889800</v>
-      </c>
-      <c r="D8" t="n">
-        <v>13732954.96</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1789685.25</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>36435.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>70828.03999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>9063450</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11254320</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13082019.96</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1331668.3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>67460.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>92249.12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6054048</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5128200</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6458389.15</v>
-      </c>
-      <c r="E10" t="n">
-        <v>288519.84</v>
-      </c>
-      <c r="F10" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>51615</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>47787.66</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>4277790</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1940400</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2523767.54</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8325</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>11304</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2352042</v>
-      </c>
-      <c r="C12" t="n">
-        <v>471240</v>
-      </c>
-      <c r="D12" t="n">
-        <v>632356.35</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5550</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1428966</v>
-      </c>
-      <c r="C13" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D13" t="n">
-        <v>342902.54</v>
-      </c>
-      <c r="E13" t="n">
-        <v>87749.83</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>986436</v>
-      </c>
-      <c r="C14" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>195015.66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>651420</v>
-      </c>
-      <c r="C15" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D15" t="n">
-        <v>158259.63</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>763884</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>784476</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>290268</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>80982</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>29502</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>35636.31</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3646440</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2865060</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1043100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" t="n">
-        <v>107280</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13650</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>343140</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11607.84</v>
-      </c>
-      <c r="C5" t="n">
-        <v>782712</v>
-      </c>
-      <c r="D5" t="n">
-        <v>614988</v>
-      </c>
-      <c r="E5" t="n">
-        <v>241200</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>30300</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2910</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>110880</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1142.46</v>
-      </c>
-      <c r="C6" t="n">
-        <v>109872</v>
-      </c>
-      <c r="D6" t="n">
-        <v>86328</v>
-      </c>
-      <c r="E6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4110</v>
-      </c>
-      <c r="H6" t="n">
-        <v>330</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>18780</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>150.21</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26712</v>
-      </c>
-      <c r="D7" t="n">
-        <v>20988</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>780</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2940</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D8" t="n">
-        <v>792</v>
-      </c>
-      <c r="E8" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5223.53</v>
-      </c>
-      <c r="C5" t="n">
-        <v>430491.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>203561.03</v>
-      </c>
-      <c r="E5" t="n">
-        <v>26604.36</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1047.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>23284.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>913.97</v>
-      </c>
-      <c r="C6" t="n">
-        <v>98884.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>43768.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5323.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6948.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>142.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26712</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13390.34</v>
-      </c>
-      <c r="E7" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>117</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D8" t="n">
-        <v>582.91</v>
-      </c>
-      <c r="E8" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>340.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11491761.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>23677038</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20626838.97</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4901587.29</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7500.06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>289818.54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>219342.82</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2010729.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5438664</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4435041.43</v>
-      </c>
-      <c r="E6" t="n">
-        <v>980801.64</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3801.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>52037.86</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>65455.81</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>313938.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1469160</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1356843.56</v>
-      </c>
-      <c r="E7" t="n">
-        <v>141076.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2164.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>16616.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>27126</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D8" t="n">
-        <v>59066.47</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40674.66</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3246.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3210.34</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
@@ -538,7 +538,7 @@
         <v>60150</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>39</v>
@@ -576,7 +576,7 @@
         <v>54270</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>25</v>
@@ -614,7 +614,7 @@
         <v>45660</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>14</v>
@@ -652,7 +652,7 @@
         <v>43560</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>12</v>
@@ -690,7 +690,7 @@
         <v>26850</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>8</v>
@@ -728,7 +728,7 @@
         <v>8040</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -804,7 +804,7 @@
         <v>4920</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -918,7 +918,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>3510</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>4530</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>3510</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>4530</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>971041.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>1253224.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J11" t="n">
         <v>58333</v>
@@ -3714,7 +3714,7 @@
         <v>207487.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>7140</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>6270</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>10</v>
@@ -9934,7 +9934,7 @@
         <v>7710</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -9972,7 +9972,7 @@
         <v>11730</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -10010,7 +10010,7 @@
         <v>2610</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -10124,7 +10124,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>19537.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J5" t="n">
         <v>7.5</v>
@@ -10866,7 +10866,7 @@
         <v>26026.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>7</v>
@@ -10904,7 +10904,7 @@
         <v>31798.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>8.4</v>
@@ -10942,7 +10942,7 @@
         <v>22822.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>6.8</v>
@@ -10980,7 +10980,7 @@
         <v>8040</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>4.75</v>
@@ -11056,7 +11056,7 @@
         <v>4920</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -11170,7 +11170,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2257.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -11798,7 +11798,7 @@
         <v>4394.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>8562.9</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
@@ -11874,7 +11874,7 @@
         <v>2218.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
@@ -11988,7 +11988,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>624454.38</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>174999</v>
@@ -12730,7 +12730,7 @@
         <v>1215793.75</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>174999</v>
@@ -12768,7 +12768,7 @@
         <v>2368926.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>40833.1</v>
@@ -12806,7 +12806,7 @@
         <v>613748.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>99166.10000000001</v>
@@ -12920,7 +12920,7 @@
         <v>8299.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>13650</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -16420,7 +16420,7 @@
         <v>5404966.38</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>287497.5</v>
       </c>
       <c r="J5" t="n">
         <v>437497.5</v>
@@ -16458,7 +16458,7 @@
         <v>7200148.23</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>408331</v>
@@ -16496,7 +16496,7 @@
         <v>8797138.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>489997.2</v>
@@ -16534,7 +16534,7 @@
         <v>6313844.62</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>396664.4</v>
@@ -16572,7 +16572,7 @@
         <v>2224266</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>277081.75</v>
@@ -16648,7 +16648,7 @@
         <v>1361118</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1149990</v>
       </c>
       <c r="J11" t="n">
         <v>174999</v>
@@ -16762,7 +16762,7 @@
         <v>207487.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>3180</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -17466,7 +17466,7 @@
         <v>19440</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
         <v>16524</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
@@ -19330,7 +19330,7 @@
         <v>4571364.6</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>247915.25</v>
@@ -20110,7 +20110,7 @@
         <v>17520</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>14</v>
@@ -20148,7 +20148,7 @@
         <v>22560</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -21080,7 +21080,7 @@
         <v>8121.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -22012,7 +22012,7 @@
         <v>2246840.64</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
@@ -544,7 +544,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1133</v>
       </c>
       <c r="L4" t="n">
         <v>1422330</v>
@@ -582,7 +582,7 @@
         <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="L5" t="n">
         <v>893010</v>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
         <v>585630</v>
@@ -658,7 +658,7 @@
         <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
         <v>540540</v>
@@ -696,7 +696,7 @@
         <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="L8" t="n">
         <v>443850</v>
@@ -734,7 +734,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="L9" t="n">
         <v>377760</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="L10" t="n">
         <v>288570</v>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="L11" t="n">
         <v>181560</v>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="L12" t="n">
         <v>149580</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L13" t="n">
         <v>96420</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L14" t="n">
         <v>41490</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>16230</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>7200</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>2310</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
         <v>17070</v>
@@ -1514,7 +1514,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>21420</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L6" t="n">
         <v>22770</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
         <v>27870</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L8" t="n">
         <v>37440</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
         <v>47100</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>43920</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>57360</v>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
         <v>92130</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
         <v>68280</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
         <v>32370</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>13170</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>5910</v>
@@ -2446,7 +2446,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="L5" t="n">
         <v>4498.2</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
         <v>8424.9</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="L7" t="n">
         <v>16722</v>
@@ -2560,7 +2560,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="L8" t="n">
         <v>26582.4</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
         <v>38151</v>
@@ -2636,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>39088.8</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>57360</v>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
         <v>92130</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
         <v>68280</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
         <v>32370</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>13170</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>5910</v>
@@ -3378,7 +3378,7 @@
         <v>52499.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71682.24000000001</v>
       </c>
       <c r="L5" t="n">
         <v>42373.04</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>277342</v>
       </c>
       <c r="L6" t="n">
         <v>79362.56</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>349877.6</v>
       </c>
       <c r="L7" t="n">
         <v>157521.24</v>
@@ -3492,7 +3492,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>403212.6</v>
       </c>
       <c r="L8" t="n">
         <v>250406.21</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L9" t="n">
         <v>359382.42</v>
@@ -3568,7 +3568,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>405346</v>
       </c>
       <c r="L10" t="n">
         <v>368216.5</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>704022</v>
       </c>
       <c r="L11" t="n">
         <v>540331.2</v>
@@ -3644,7 +3644,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>768024</v>
       </c>
       <c r="L12" t="n">
         <v>867864.6</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>682688</v>
       </c>
       <c r="L13" t="n">
         <v>643197.6</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>426680</v>
       </c>
       <c r="L14" t="n">
         <v>304925.4</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L15" t="n">
         <v>124061.4</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L16" t="n">
         <v>55672.2</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L4" t="n">
         <v>144900</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
         <v>57840</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>11280</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>3090</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12.18</v>
       </c>
       <c r="L5" t="n">
         <v>12146.4</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>4173.6</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1854</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>259848.12</v>
       </c>
       <c r="L5" t="n">
         <v>114419.09</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>39315.31</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>17464.68</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="L4" t="n">
         <v>138000</v>
@@ -7106,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L5" t="n">
         <v>48090</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>13800</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>3780</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2040</v>
@@ -8038,7 +8038,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19.74</v>
       </c>
       <c r="L5" t="n">
         <v>10098.9</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>5106</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>2268</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1448.4</v>
@@ -8970,7 +8970,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>421133.16</v>
       </c>
       <c r="L5" t="n">
         <v>95131.64</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>124803.9</v>
       </c>
       <c r="L6" t="n">
         <v>48098.52</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>21364.56</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>13643.93</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="L4" t="n">
         <v>172020</v>
@@ -9902,7 +9902,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="L5" t="n">
         <v>164670</v>
@@ -9940,7 +9940,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L6" t="n">
         <v>158550</v>
@@ -9978,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="L7" t="n">
         <v>202890</v>
@@ -10016,7 +10016,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="L8" t="n">
         <v>124650</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9" t="n">
         <v>73080</v>
@@ -10092,7 +10092,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L10" t="n">
         <v>38430</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>9450</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>4470</v>
@@ -10834,7 +10834,7 @@
         <v>7.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>260.4</v>
       </c>
       <c r="L5" t="n">
         <v>187532.1</v>
@@ -10872,7 +10872,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>279.5</v>
       </c>
       <c r="L6" t="n">
         <v>216683.1</v>
@@ -10910,7 +10910,7 @@
         <v>8.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>376.38</v>
       </c>
       <c r="L7" t="n">
         <v>324324</v>
@@ -10948,7 +10948,7 @@
         <v>6.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3</v>
       </c>
       <c r="L8" t="n">
         <v>315133.5</v>
@@ -10986,7 +10986,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="L9" t="n">
         <v>305985.6</v>
@@ -11024,7 +11024,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="L10" t="n">
         <v>256827.3</v>
@@ -11062,7 +11062,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="L11" t="n">
         <v>181560</v>
@@ -11100,7 +11100,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="L12" t="n">
         <v>149580</v>
@@ -11138,7 +11138,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L13" t="n">
         <v>96420</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L14" t="n">
         <v>41490</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>16230</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>7200</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>2310</v>
@@ -11766,7 +11766,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>66.78</v>
       </c>
       <c r="L5" t="n">
         <v>34580.7</v>
@@ -11804,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="L6" t="n">
         <v>58663.5</v>
@@ -11842,7 +11842,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>171.38</v>
       </c>
       <c r="L7" t="n">
         <v>121734</v>
@@ -11880,7 +11880,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>109.8</v>
       </c>
       <c r="L8" t="n">
         <v>88501.5</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9" t="n">
         <v>59194.8</v>
@@ -11956,7 +11956,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L10" t="n">
         <v>34202.7</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>9450</v>
@@ -12032,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>4470</v>
@@ -12698,7 +12698,7 @@
         <v>174999</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1424684.52</v>
       </c>
       <c r="L5" t="n">
         <v>325750.19</v>
@@ -12736,7 +12736,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2080065</v>
       </c>
       <c r="L6" t="n">
         <v>552610.17</v>
@@ -12774,7 +12774,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3656220.92</v>
       </c>
       <c r="L7" t="n">
         <v>1146734.28</v>
@@ -12812,7 +12812,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2342473.2</v>
       </c>
       <c r="L8" t="n">
         <v>833684.13</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1920060</v>
       </c>
       <c r="L9" t="n">
         <v>557615.02</v>
@@ -12888,7 +12888,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>938696</v>
       </c>
       <c r="L10" t="n">
         <v>322189.43</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>106670</v>
       </c>
       <c r="L11" t="n">
         <v>89019</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L12" t="n">
         <v>42107.4</v>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="L4" t="n">
         <v>343140</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>110880</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.44</v>
       </c>
       <c r="L5" t="n">
         <v>23284.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>286728.96</v>
       </c>
       <c r="L5" t="n">
         <v>219342.82</v>
@@ -16426,7 +16426,7 @@
         <v>437497.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5555373.6</v>
       </c>
       <c r="L5" t="n">
         <v>1766552.38</v>
@@ -16464,7 +16464,7 @@
         <v>408331</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5962853</v>
       </c>
       <c r="L6" t="n">
         <v>2041154.8</v>
@@ -16502,7 +16502,7 @@
         <v>489997.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8029690.92</v>
       </c>
       <c r="L7" t="n">
         <v>3055132.08</v>
@@ -16540,7 +16540,7 @@
         <v>396664.4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6854614.2</v>
       </c>
       <c r="L8" t="n">
         <v>2968557.57</v>
@@ -16578,7 +16578,7 @@
         <v>277081.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7061554</v>
       </c>
       <c r="L9" t="n">
         <v>2882384.35</v>
@@ -16616,7 +16616,7 @@
         <v>641663</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5568174</v>
       </c>
       <c r="L10" t="n">
         <v>2419313.17</v>
@@ -16654,7 +16654,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3520110</v>
       </c>
       <c r="L11" t="n">
         <v>1710295.2</v>
@@ -16692,7 +16692,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2261404</v>
       </c>
       <c r="L12" t="n">
         <v>1409043.6</v>
@@ -16730,7 +16730,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1173370</v>
       </c>
       <c r="L13" t="n">
         <v>908276.4</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L14" t="n">
         <v>390835.8</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L15" t="n">
         <v>152886.6</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L16" t="n">
         <v>67824</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>21760.2</v>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="L4" t="n">
         <v>140520</v>
@@ -17358,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="L5" t="n">
         <v>166830</v>
@@ -17396,7 +17396,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="L6" t="n">
         <v>173490</v>
@@ -17434,7 +17434,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L7" t="n">
         <v>185190</v>
@@ -17472,7 +17472,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="L8" t="n">
         <v>240090</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="L9" t="n">
         <v>240030</v>
@@ -17548,7 +17548,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="L10" t="n">
         <v>198330</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="L11" t="n">
         <v>112530</v>
@@ -17624,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L12" t="n">
         <v>52140</v>
@@ -17662,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L13" t="n">
         <v>25110</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>7740</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1020</v>
@@ -17814,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -18290,7 +18290,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>35034.3</v>
@@ -18328,7 +18328,7 @@
         <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>64191.3</v>
@@ -18366,7 +18366,7 @@
         <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>123.82</v>
       </c>
       <c r="L7" t="n">
         <v>111114</v>
@@ -18404,7 +18404,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>182.7</v>
       </c>
       <c r="L8" t="n">
         <v>170463.9</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="L9" t="n">
         <v>194424.3</v>
@@ -18480,7 +18480,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="L10" t="n">
         <v>176513.7</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="L11" t="n">
         <v>112530</v>
@@ -18556,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L12" t="n">
         <v>52140</v>
@@ -18594,7 +18594,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L13" t="n">
         <v>25110</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>7740</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1020</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -19222,7 +19222,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1379883.12</v>
       </c>
       <c r="L5" t="n">
         <v>330023.11</v>
@@ -19260,7 +19260,7 @@
         <v>145832.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1955261.1</v>
       </c>
       <c r="L6" t="n">
         <v>604682.05</v>
@@ -19298,7 +19298,7 @@
         <v>326664.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2641575.88</v>
       </c>
       <c r="L7" t="n">
         <v>1046693.88</v>
@@ -19336,7 +19336,7 @@
         <v>247915.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3897721.8</v>
       </c>
       <c r="L8" t="n">
         <v>1605769.94</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4522808</v>
       </c>
       <c r="L9" t="n">
         <v>1831476.91</v>
@@ -19412,7 +19412,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4202798</v>
       </c>
       <c r="L10" t="n">
         <v>1662759.05</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2709418</v>
       </c>
       <c r="L11" t="n">
         <v>1060032.6</v>
@@ -19488,7 +19488,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1450712</v>
       </c>
       <c r="L12" t="n">
         <v>491158.8</v>
@@ -19526,7 +19526,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>469348</v>
       </c>
       <c r="L13" t="n">
         <v>236536.2</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>170672</v>
       </c>
       <c r="L14" t="n">
         <v>72910.8</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>9608.4</v>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>1130.4</v>
@@ -20116,7 +20116,7 @@
         <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="L4" t="n">
         <v>408210</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="L5" t="n">
         <v>261990</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L6" t="n">
         <v>134580</v>
@@ -20230,7 +20230,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L7" t="n">
         <v>79140</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>21810</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="L5" t="n">
         <v>55017.9</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="L6" t="n">
         <v>49794.6</v>
@@ -21162,7 +21162,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>60.68</v>
       </c>
       <c r="L7" t="n">
         <v>47484</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
         <v>15485.1</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1702453.2</v>
       </c>
       <c r="L5" t="n">
         <v>518268.62</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1497646.8</v>
       </c>
       <c r="L6" t="n">
         <v>469065.13</v>
@@ -22094,7 +22094,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1294547.12</v>
       </c>
       <c r="L7" t="n">
         <v>447299.28</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>172805.4</v>
       </c>
       <c r="L8" t="n">
         <v>145869.64</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
@@ -549,7 +549,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>1113</v>
+        <v>435</v>
       </c>
       <c r="L4" t="n">
         <v>1419210</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>607</v>
+        <v>258</v>
       </c>
       <c r="L5" t="n">
         <v>891060</v>
@@ -631,7 +631,7 @@
         <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>163</v>
       </c>
       <c r="L6" t="n">
         <v>583890</v>
@@ -672,7 +672,7 @@
         <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>458</v>
+        <v>155</v>
       </c>
       <c r="L7" t="n">
         <v>539490</v>
@@ -713,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>357</v>
+        <v>102</v>
       </c>
       <c r="L8" t="n">
         <v>443130</v>
@@ -754,7 +754,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="L9" t="n">
         <v>377400</v>
@@ -795,7 +795,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>261</v>
+        <v>57</v>
       </c>
       <c r="L10" t="n">
         <v>288480</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="L11" t="n">
         <v>181290</v>
@@ -877,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
         <v>149370</v>
@@ -918,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>96420</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>41490</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>16230</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>7200</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2310</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>17220</v>
@@ -1594,7 +1594,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>21390</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>22830</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>27990</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
         <v>37650</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
         <v>47220</v>
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>43950</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>57600</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>92250</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>68340</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>32430</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>13200</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>5910</v>
@@ -2598,7 +2598,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.32</v>
+        <v>1.32</v>
       </c>
       <c r="L5" t="n">
         <v>4491.9</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10.14</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>8447.1</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.76</v>
+        <v>6.38</v>
       </c>
       <c r="L7" t="n">
         <v>16794</v>
@@ -2721,7 +2721,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>15.46</v>
+        <v>9.57</v>
       </c>
       <c r="L8" t="n">
         <v>26731.5</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>20.88</v>
+        <v>7.23</v>
       </c>
       <c r="L9" t="n">
         <v>38248.2</v>
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>16.53</v>
+        <v>2.61</v>
       </c>
       <c r="L10" t="n">
         <v>39115.5</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>29.65</v>
+        <v>3.59</v>
       </c>
       <c r="L11" t="n">
         <v>57600</v>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>33.37</v>
+        <v>3.71</v>
       </c>
       <c r="L12" t="n">
         <v>92250</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>30.38</v>
+        <v>4.75</v>
       </c>
       <c r="L13" t="n">
         <v>68340</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>19.44</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>32430</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>9.859999999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>13200</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>5910</v>
@@ -3602,7 +3602,7 @@
         <v>21850.2</v>
       </c>
       <c r="K5" t="n">
-        <v>112504.25</v>
+        <v>64288.14</v>
       </c>
       <c r="L5" t="n">
         <v>808542</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>492357.84</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
         <v>1520478</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>619574.5600000001</v>
+        <v>309787.28</v>
       </c>
       <c r="L7" t="n">
         <v>3022920</v>
@@ -3725,7 +3725,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>750481.54</v>
+        <v>464583.81</v>
       </c>
       <c r="L8" t="n">
         <v>4811670</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1013752.17</v>
+        <v>350914.21</v>
       </c>
       <c r="L9" t="n">
         <v>6884676</v>
@@ -3807,7 +3807,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>802630.6800000001</v>
+        <v>126731.16</v>
       </c>
       <c r="L10" t="n">
         <v>7040790</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1439709.68</v>
+        <v>174510.26</v>
       </c>
       <c r="L11" t="n">
         <v>10368000</v>
@@ -3889,7 +3889,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>1620410.83</v>
+        <v>180045.65</v>
       </c>
       <c r="L12" t="n">
         <v>16605000</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1475325.5</v>
+        <v>230519.61</v>
       </c>
       <c r="L13" t="n">
         <v>12301200</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>943928.64</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>5837400</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>478762.16</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2376000</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1063800</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>144780</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>58530</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>11220</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9.6</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
         <v>12291.3</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>4151.4</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>466089.04</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
         <v>2212434</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>747252</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>138210</v>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>48660</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>13890</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3780</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2040</v>
@@ -8622,7 +8622,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>15.56</v>
+        <v>3.31</v>
       </c>
       <c r="L5" t="n">
         <v>10218.6</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>5139.3</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2268</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1448.4</v>
@@ -9626,7 +9626,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>755385.6899999999</v>
+        <v>160720.36</v>
       </c>
       <c r="L5" t="n">
         <v>1839348</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>221561.03</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>925074</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>408240</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>260712</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="L4" t="n">
         <v>172410</v>
@@ -10630,7 +10630,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
         <v>164760</v>
@@ -10671,7 +10671,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="L6" t="n">
         <v>158640</v>
@@ -10712,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>209</v>
+        <v>74</v>
       </c>
       <c r="L7" t="n">
         <v>202980</v>
@@ -10753,7 +10753,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
         <v>124680</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
         <v>73140</v>
@@ -10835,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>38430</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>9450</v>
@@ -11634,7 +11634,7 @@
         <v>7.5</v>
       </c>
       <c r="K5" t="n">
-        <v>200.92</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>187122.6</v>
@@ -11675,7 +11675,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>215.48</v>
+        <v>82.64</v>
       </c>
       <c r="L6" t="n">
         <v>216039.3</v>
@@ -11716,7 +11716,7 @@
         <v>8.4</v>
       </c>
       <c r="K7" t="n">
-        <v>292.2</v>
+        <v>98.89</v>
       </c>
       <c r="L7" t="n">
         <v>323694</v>
@@ -11757,7 +11757,7 @@
         <v>6.8</v>
       </c>
       <c r="K8" t="n">
-        <v>262.75</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>314622.3</v>
@@ -11798,7 +11798,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>265.79</v>
+        <v>88.33</v>
       </c>
       <c r="L9" t="n">
         <v>305694</v>
@@ -11839,7 +11839,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>227.07</v>
+        <v>49.59</v>
       </c>
       <c r="L10" t="n">
         <v>256747.2</v>
@@ -11880,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>148.25</v>
+        <v>31.45</v>
       </c>
       <c r="L11" t="n">
         <v>181290</v>
@@ -11921,7 +11921,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>98.26000000000001</v>
+        <v>11.12</v>
       </c>
       <c r="L12" t="n">
         <v>149370</v>
@@ -11962,7 +11962,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>52.22</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
         <v>96420</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27.22</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>41490</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>9.859999999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>16230</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>7200</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2310</v>
@@ -12638,7 +12638,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>52.63</v>
+        <v>28.47</v>
       </c>
       <c r="L5" t="n">
         <v>34599.6</v>
@@ -12679,7 +12679,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>76.05</v>
+        <v>37.52</v>
       </c>
       <c r="L6" t="n">
         <v>58696.8</v>
@@ -12720,7 +12720,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>133.34</v>
+        <v>47.21</v>
       </c>
       <c r="L7" t="n">
         <v>121788</v>
@@ -12761,7 +12761,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>89.79000000000001</v>
+        <v>29.44</v>
       </c>
       <c r="L8" t="n">
         <v>88522.8</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>72.27</v>
+        <v>27.3</v>
       </c>
       <c r="L9" t="n">
         <v>59243.4</v>
@@ -12843,7 +12843,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>39.15</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>34202.7</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.49</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>9450</v>
@@ -13642,7 +13642,7 @@
         <v>72834</v>
       </c>
       <c r="K5" t="n">
-        <v>2555453.72</v>
+        <v>1382195.1</v>
       </c>
       <c r="L5" t="n">
         <v>6227928</v>
@@ -13683,7 +13683,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>3692683.8</v>
+        <v>1821724.01</v>
       </c>
       <c r="L6" t="n">
         <v>10565424</v>
@@ -13724,7 +13724,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>6474554.15</v>
+        <v>2292425.87</v>
       </c>
       <c r="L7" t="n">
         <v>21921840</v>
@@ -13765,7 +13765,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4359940.35</v>
+        <v>1429488.64</v>
       </c>
       <c r="L8" t="n">
         <v>15934104</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3509142.12</v>
+        <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
         <v>10663812</v>
@@ -13847,7 +13847,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>1900967.4</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
         <v>6156486</v>
@@ -13888,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>218137.83</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
         <v>1701000</v>
@@ -14605,7 +14605,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="L4" t="n">
         <v>345630</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>111990</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.59</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
         <v>23517.9</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>514305.15</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
         <v>4233222</v>
@@ -17658,7 +17658,7 @@
         <v>182085</v>
       </c>
       <c r="K5" t="n">
-        <v>9755725.85</v>
+        <v>4146585.29</v>
       </c>
       <c r="L5" t="n">
         <v>33682068</v>
@@ -17699,7 +17699,7 @@
         <v>169946</v>
       </c>
       <c r="K6" t="n">
-        <v>10462604.1</v>
+        <v>4012716.4</v>
       </c>
       <c r="L6" t="n">
         <v>38887074</v>
@@ -17740,7 +17740,7 @@
         <v>203935.2</v>
       </c>
       <c r="K7" t="n">
-        <v>14188257.42</v>
+        <v>4801702.84</v>
       </c>
       <c r="L7" t="n">
         <v>58264920</v>
@@ -17781,7 +17781,7 @@
         <v>165090.4</v>
       </c>
       <c r="K8" t="n">
-        <v>12758186.11</v>
+        <v>3645196.03</v>
       </c>
       <c r="L8" t="n">
         <v>56632014</v>
@@ -17822,7 +17822,7 @@
         <v>115320.5</v>
       </c>
       <c r="K9" t="n">
-        <v>12905844.91</v>
+        <v>4288951.48</v>
       </c>
       <c r="L9" t="n">
         <v>55024920</v>
@@ -17863,7 +17863,7 @@
         <v>267058</v>
       </c>
       <c r="K10" t="n">
-        <v>11025610.92</v>
+        <v>2407892.04</v>
       </c>
       <c r="L10" t="n">
         <v>46214496</v>
@@ -17904,7 +17904,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>7198548.39</v>
+        <v>1526964.81</v>
       </c>
       <c r="L11" t="n">
         <v>32632200</v>
@@ -17945,7 +17945,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>4771209.67</v>
+        <v>540136.9399999999</v>
       </c>
       <c r="L12" t="n">
         <v>26886600</v>
@@ -17986,7 +17986,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>2535715.71</v>
+        <v>276623.53</v>
       </c>
       <c r="L13" t="n">
         <v>17355600</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1321500.1</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>7468200</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>478762.16</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2921400</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>194224</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1296000</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>415800</v>
@@ -18621,7 +18621,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
         <v>137520</v>
@@ -18662,7 +18662,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>142</v>
+        <v>68</v>
       </c>
       <c r="L5" t="n">
         <v>165330</v>
@@ -18703,7 +18703,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="L6" t="n">
         <v>172830</v>
@@ -18744,7 +18744,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="L7" t="n">
         <v>184440</v>
@@ -18785,7 +18785,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="L8" t="n">
         <v>239370</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="L9" t="n">
         <v>239700</v>
@@ -18867,7 +18867,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>197</v>
+        <v>49</v>
       </c>
       <c r="L10" t="n">
         <v>198300</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>112320</v>
@@ -18949,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>51960</v>
@@ -18990,7 +18990,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>25200</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>7740</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1020</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -19666,7 +19666,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>47</v>
+        <v>22.51</v>
       </c>
       <c r="L5" t="n">
         <v>34719.3</v>
@@ -19707,7 +19707,7 @@
         <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>68.95</v>
+        <v>27.38</v>
       </c>
       <c r="L6" t="n">
         <v>63947.1</v>
@@ -19748,7 +19748,7 @@
         <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>95.7</v>
+        <v>37</v>
       </c>
       <c r="L7" t="n">
         <v>110664</v>
@@ -19789,7 +19789,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>149.41</v>
+        <v>35.33</v>
       </c>
       <c r="L8" t="n">
         <v>169952.7</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>170.24</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
         <v>194157</v>
@@ -19871,7 +19871,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>171.39</v>
+        <v>42.63</v>
       </c>
       <c r="L10" t="n">
         <v>176487</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>114.11</v>
+        <v>26.06</v>
       </c>
       <c r="L11" t="n">
         <v>112320</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>63.04</v>
+        <v>5.56</v>
       </c>
       <c r="L12" t="n">
         <v>51960</v>
@@ -19994,7 +19994,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>21.84</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>25200</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>7.78</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>7740</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1020</v>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>120</v>
@@ -20670,7 +20670,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2282229.11</v>
+        <v>1092898.45</v>
       </c>
       <c r="L5" t="n">
         <v>6249474</v>
@@ -20711,7 +20711,7 @@
         <v>60695</v>
       </c>
       <c r="K6" t="n">
-        <v>3348033.31</v>
+        <v>1329366.17</v>
       </c>
       <c r="L6" t="n">
         <v>11510478</v>
@@ -20752,7 +20752,7 @@
         <v>135956.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4646809.2</v>
+        <v>1796766.22</v>
       </c>
       <c r="L7" t="n">
         <v>19919520</v>
@@ -20793,7 +20793,7 @@
         <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>7254654.85</v>
+        <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
         <v>30591486</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>8265979.22</v>
+        <v>2573370.89</v>
       </c>
       <c r="L9" t="n">
         <v>34948260</v>
@@ -20875,7 +20875,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>8322012.84</v>
+        <v>2069942.28</v>
       </c>
       <c r="L10" t="n">
         <v>31767660</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>5540700.88</v>
+        <v>1265199.41</v>
       </c>
       <c r="L11" t="n">
         <v>20217600</v>
@@ -20957,7 +20957,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3060776.02</v>
+        <v>270068.47</v>
       </c>
       <c r="L12" t="n">
         <v>9352800</v>
@@ -20998,7 +20998,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>1060390.21</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>4536000</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>377571.46</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1393200</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>183600</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>21600</v>
@@ -21633,7 +21633,7 @@
         <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>97</v>
       </c>
       <c r="L4" t="n">
         <v>406980</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>260910</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
         <v>135180</v>
@@ -21756,7 +21756,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
         <v>79080</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>21900</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>62.89</v>
+        <v>19.86</v>
       </c>
       <c r="L5" t="n">
         <v>54791.1</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>54.76</v>
+        <v>13.69</v>
       </c>
       <c r="L6" t="n">
         <v>50016.6</v>
@@ -22760,7 +22760,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>47.21</v>
+        <v>7.66</v>
       </c>
       <c r="L7" t="n">
         <v>47448</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.62</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>15549</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3053686.84</v>
+        <v>964322.16</v>
       </c>
       <c r="L5" t="n">
         <v>9862398</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2658732.34</v>
+        <v>664683.08</v>
       </c>
       <c r="L6" t="n">
         <v>9002988</v>
@@ -23764,7 +23764,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2292425.87</v>
+        <v>371744.74</v>
       </c>
       <c r="L7" t="n">
         <v>8540640</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321634.94</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
         <v>2798820</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_RedCapacity.xlsx
@@ -560,7 +560,7 @@
         <v>543660</v>
       </c>
       <c r="H4" t="n">
-        <v>60150</v>
+        <v>67350</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -572,22 +572,22 @@
         <v>435</v>
       </c>
       <c r="L4" t="n">
-        <v>1419210</v>
+        <v>1517730</v>
       </c>
       <c r="M4" t="n">
-        <v>71250</v>
+        <v>50070</v>
       </c>
       <c r="N4" t="n">
-        <v>80940</v>
+        <v>77370</v>
       </c>
       <c r="O4" t="n">
-        <v>222570</v>
+        <v>223920</v>
       </c>
       <c r="P4" t="n">
-        <v>42000</v>
+        <v>15420</v>
       </c>
       <c r="Q4" t="n">
-        <v>215932.27</v>
+        <v>2237685.25</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>353400</v>
       </c>
       <c r="H5" t="n">
-        <v>54270</v>
+        <v>58770</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -625,22 +625,22 @@
         <v>258</v>
       </c>
       <c r="L5" t="n">
-        <v>891060</v>
+        <v>942900</v>
       </c>
       <c r="M5" t="n">
-        <v>51600</v>
+        <v>37470</v>
       </c>
       <c r="N5" t="n">
-        <v>75330</v>
+        <v>87390</v>
       </c>
       <c r="O5" t="n">
-        <v>182160</v>
+        <v>209130</v>
       </c>
       <c r="P5" t="n">
-        <v>52920</v>
+        <v>34080</v>
       </c>
       <c r="Q5" t="n">
-        <v>137563.63</v>
+        <v>1425558.57</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>238410</v>
       </c>
       <c r="H6" t="n">
-        <v>45660</v>
+        <v>46260</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>163</v>
       </c>
       <c r="L6" t="n">
-        <v>583890</v>
+        <v>583950</v>
       </c>
       <c r="M6" t="n">
-        <v>34560</v>
+        <v>23130</v>
       </c>
       <c r="N6" t="n">
-        <v>25800</v>
+        <v>36180</v>
       </c>
       <c r="O6" t="n">
-        <v>114270</v>
+        <v>123900</v>
       </c>
       <c r="P6" t="n">
-        <v>51690</v>
+        <v>37410</v>
       </c>
       <c r="Q6" t="n">
-        <v>96179.22</v>
+        <v>996695.99</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>210360</v>
       </c>
       <c r="H7" t="n">
-        <v>43560</v>
+        <v>45720</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -731,22 +731,22 @@
         <v>155</v>
       </c>
       <c r="L7" t="n">
-        <v>539490</v>
+        <v>536970</v>
       </c>
       <c r="M7" t="n">
-        <v>24210</v>
+        <v>26580</v>
       </c>
       <c r="N7" t="n">
-        <v>9150</v>
+        <v>14100</v>
       </c>
       <c r="O7" t="n">
-        <v>84420</v>
+        <v>91020</v>
       </c>
       <c r="P7" t="n">
-        <v>62070</v>
+        <v>45240</v>
       </c>
       <c r="Q7" t="n">
-        <v>93828.14999999999</v>
+        <v>972332</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>178350</v>
       </c>
       <c r="H8" t="n">
-        <v>26850</v>
+        <v>28170</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -784,22 +784,22 @@
         <v>102</v>
       </c>
       <c r="L8" t="n">
-        <v>443130</v>
+        <v>440070</v>
       </c>
       <c r="M8" t="n">
-        <v>19290</v>
+        <v>26190</v>
       </c>
       <c r="N8" t="n">
-        <v>1650</v>
+        <v>3960</v>
       </c>
       <c r="O8" t="n">
-        <v>61170</v>
+        <v>65280</v>
       </c>
       <c r="P8" t="n">
-        <v>69030</v>
+        <v>55230</v>
       </c>
       <c r="Q8" t="n">
-        <v>78983.45</v>
+        <v>818497.84</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>162000</v>
       </c>
       <c r="H9" t="n">
-        <v>8040</v>
+        <v>10920</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -837,22 +837,22 @@
         <v>110</v>
       </c>
       <c r="L9" t="n">
-        <v>377400</v>
+        <v>395040</v>
       </c>
       <c r="M9" t="n">
-        <v>11640</v>
+        <v>34530</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O9" t="n">
-        <v>55260</v>
+        <v>65130</v>
       </c>
       <c r="P9" t="n">
-        <v>68220</v>
+        <v>62730</v>
       </c>
       <c r="Q9" t="n">
-        <v>75397.07000000001</v>
+        <v>781332.5600000001</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>133650</v>
       </c>
       <c r="H10" t="n">
-        <v>3750</v>
+        <v>3720</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>57</v>
       </c>
       <c r="L10" t="n">
-        <v>288480</v>
+        <v>320640</v>
       </c>
       <c r="M10" t="n">
-        <v>10260</v>
+        <v>24600</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>32130</v>
+        <v>45600</v>
       </c>
       <c r="P10" t="n">
-        <v>77250</v>
+        <v>76830</v>
       </c>
       <c r="Q10" t="n">
-        <v>61107.36</v>
+        <v>633249.67</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>76320</v>
       </c>
       <c r="H11" t="n">
-        <v>4920</v>
+        <v>4590</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
@@ -943,22 +943,22 @@
         <v>35</v>
       </c>
       <c r="L11" t="n">
-        <v>181290</v>
+        <v>217320</v>
       </c>
       <c r="M11" t="n">
-        <v>6210</v>
+        <v>26070</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>10890</v>
+        <v>21390</v>
       </c>
       <c r="P11" t="n">
-        <v>73080</v>
+        <v>91260</v>
       </c>
       <c r="Q11" t="n">
-        <v>38522.98</v>
+        <v>399209.92</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>59730</v>
       </c>
       <c r="H12" t="n">
-        <v>4680</v>
+        <v>5640</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>149370</v>
+        <v>198840</v>
       </c>
       <c r="M12" t="n">
-        <v>3510</v>
+        <v>22950</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4260</v>
+        <v>11940</v>
       </c>
       <c r="P12" t="n">
-        <v>58890</v>
+        <v>97800</v>
       </c>
       <c r="Q12" t="n">
-        <v>27256.85</v>
+        <v>282460.09</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>48270</v>
       </c>
       <c r="H13" t="n">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>96420</v>
+        <v>133470</v>
       </c>
       <c r="M13" t="n">
-        <v>2640</v>
+        <v>16440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2430</v>
+        <v>3870</v>
       </c>
       <c r="P13" t="n">
-        <v>42180</v>
+        <v>70350</v>
       </c>
       <c r="Q13" t="n">
-        <v>18676.15</v>
+        <v>193539.12</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>22260</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1102,22 +1102,22 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>41490</v>
+        <v>57960</v>
       </c>
       <c r="M14" t="n">
-        <v>1170</v>
+        <v>16890</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3480</v>
+        <v>3150</v>
       </c>
       <c r="P14" t="n">
-        <v>28320</v>
+        <v>36720</v>
       </c>
       <c r="Q14" t="n">
-        <v>8832.25</v>
+        <v>91527.72</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>5520</v>
       </c>
       <c r="H15" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16230</v>
+        <v>30420</v>
       </c>
       <c r="M15" t="n">
-        <v>300</v>
+        <v>6090</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>780</v>
+        <v>1350</v>
       </c>
       <c r="P15" t="n">
-        <v>30150</v>
+        <v>33360</v>
       </c>
       <c r="Q15" t="n">
-        <v>3171.34</v>
+        <v>32864.26</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>3780</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7200</v>
+        <v>24150</v>
       </c>
       <c r="M16" t="n">
+        <v>3150</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>150</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>30</v>
-      </c>
       <c r="P16" t="n">
-        <v>38610</v>
+        <v>55590</v>
       </c>
       <c r="Q16" t="n">
-        <v>2198.63</v>
+        <v>22784.21</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>1290</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2310</v>
+        <v>9480</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>1590</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>21300</v>
+        <v>32790</v>
       </c>
       <c r="Q17" t="n">
-        <v>1136.31</v>
+        <v>11775.48</v>
       </c>
     </row>
     <row r="18">
@@ -1302,7 +1302,7 @@
         <v>330</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1560</v>
+        <v>6180</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>21180</v>
+        <v>30600</v>
       </c>
       <c r="Q18" t="n">
-        <v>537.02</v>
+        <v>5565.08</v>
       </c>
     </row>
     <row r="19">
@@ -1367,22 +1367,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1410</v>
+        <v>3810</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>1230</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>17820</v>
+        <v>30990</v>
       </c>
       <c r="Q19" t="n">
-        <v>250.43</v>
+        <v>2595.19</v>
       </c>
     </row>
     <row r="20">
@@ -1408,7 +1408,7 @@
         <v>3630</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>600</v>
+        <v>3150</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2010</v>
+        <v>5370</v>
       </c>
       <c r="Q20" t="n">
-        <v>74.44</v>
+        <v>771.39</v>
       </c>
     </row>
     <row r="21">
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.73</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.67</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="23">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>7920</v>
       </c>
       <c r="H4" t="n">
-        <v>3480</v>
+        <v>3600</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>17220</v>
+        <v>17490</v>
       </c>
       <c r="M4" t="n">
-        <v>3510</v>
+        <v>1590</v>
       </c>
       <c r="N4" t="n">
-        <v>1140</v>
+        <v>450</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>121.01</v>
+        <v>13714.92</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>9360</v>
       </c>
       <c r="H5" t="n">
-        <v>4080</v>
+        <v>4800</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>21390</v>
+        <v>17940</v>
       </c>
       <c r="M5" t="n">
-        <v>8160</v>
+        <v>5010</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="O5" t="n">
         <v>30</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>244.7</v>
+        <v>27732.78</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>8280</v>
       </c>
       <c r="H6" t="n">
-        <v>2880</v>
+        <v>3480</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>22830</v>
+        <v>18390</v>
       </c>
       <c r="M6" t="n">
-        <v>9960</v>
+        <v>5040</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>589.41</v>
+        <v>66799.8</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>8640</v>
       </c>
       <c r="H7" t="n">
-        <v>3690</v>
+        <v>3300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>27990</v>
+        <v>21210</v>
       </c>
       <c r="M7" t="n">
-        <v>7710</v>
+        <v>3930</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>870</v>
+        <v>750</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>973.62</v>
+        <v>110343.6</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>15480</v>
       </c>
       <c r="H8" t="n">
-        <v>3720</v>
+        <v>2940</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,10 +2076,10 @@
         <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>37650</v>
+        <v>33000</v>
       </c>
       <c r="M8" t="n">
-        <v>6630</v>
+        <v>2400</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1256.96</v>
+        <v>142455.24</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>20010</v>
       </c>
       <c r="H9" t="n">
-        <v>3510</v>
+        <v>4980</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -2129,22 +2129,22 @@
         <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>47220</v>
+        <v>43860</v>
       </c>
       <c r="M9" t="n">
-        <v>3540</v>
+        <v>2520</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1286.36</v>
+        <v>145787.58</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>17640</v>
       </c>
       <c r="H10" t="n">
-        <v>3240</v>
+        <v>3030</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,22 +2182,22 @@
         <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>43950</v>
+        <v>45750</v>
       </c>
       <c r="M10" t="n">
-        <v>3000</v>
+        <v>1140</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1296.38</v>
+        <v>146922.84</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>19590</v>
       </c>
       <c r="H11" t="n">
-        <v>4530</v>
+        <v>3930</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -2235,22 +2235,22 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>57600</v>
+        <v>53730</v>
       </c>
       <c r="M11" t="n">
-        <v>2010</v>
+        <v>3540</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1222.15</v>
+        <v>138510.9</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>32550</v>
       </c>
       <c r="H12" t="n">
-        <v>4620</v>
+        <v>5220</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,22 +2288,22 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>92250</v>
+        <v>95130</v>
       </c>
       <c r="M12" t="n">
-        <v>1020</v>
+        <v>4380</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1805.41</v>
+        <v>204613.02</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>28320</v>
       </c>
       <c r="H13" t="n">
-        <v>1440</v>
+        <v>1860</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>68340</v>
+        <v>78570</v>
       </c>
       <c r="M13" t="n">
-        <v>300</v>
+        <v>3780</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1798.09</v>
+        <v>203783.76</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>15240</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>32430</v>
+        <v>38820</v>
       </c>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>3720</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1001.02</v>
+        <v>113449.5</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>4350</v>
       </c>
       <c r="H15" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>13200</v>
+        <v>19170</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>388.42</v>
+        <v>44021.16</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>3060</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5910</v>
+        <v>12000</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>286.88</v>
+        <v>32512.5</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>570</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1800</v>
+        <v>4170</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>12692.88</v>
       </c>
     </row>
     <row r="18">
@@ -2594,7 +2594,7 @@
         <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>990</v>
+        <v>2100</v>
       </c>
       <c r="M18" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>54</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="19">
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19.36</v>
+        <v>2194.02</v>
       </c>
     </row>
     <row r="20">
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2712,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>600</v>
+        <v>2940</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.289999999999999</v>
+        <v>939.42</v>
       </c>
     </row>
     <row r="21">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.59</v>
+        <v>180.54</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.38</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="23">
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1468.8</v>
+        <v>1728</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,13 +3209,13 @@
         <v>1.32</v>
       </c>
       <c r="L5" t="n">
-        <v>4491.9</v>
+        <v>3767.4</v>
       </c>
       <c r="M5" t="n">
-        <v>163.2</v>
+        <v>100.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.24</v>
+        <v>1386.64</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>414</v>
       </c>
       <c r="H6" t="n">
-        <v>1641.6</v>
+        <v>1983.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>4.06</v>
       </c>
       <c r="L6" t="n">
-        <v>8447.1</v>
+        <v>6804.3</v>
       </c>
       <c r="M6" t="n">
-        <v>796.8</v>
+        <v>403.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>442.06</v>
+        <v>50099.85</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1296</v>
       </c>
       <c r="H7" t="n">
-        <v>2693.7</v>
+        <v>2409</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>6.38</v>
       </c>
       <c r="L7" t="n">
-        <v>16794</v>
+        <v>12726</v>
       </c>
       <c r="M7" t="n">
-        <v>2698.5</v>
+        <v>1375.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>304.5</v>
+        <v>262.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>778.9</v>
+        <v>88274.88</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>10062</v>
       </c>
       <c r="H8" t="n">
-        <v>3162</v>
+        <v>2499</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>9.57</v>
       </c>
       <c r="L8" t="n">
-        <v>26731.5</v>
+        <v>23430</v>
       </c>
       <c r="M8" t="n">
-        <v>3646.5</v>
+        <v>1320</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1194.11</v>
+        <v>135332.48</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>17008.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3510</v>
+        <v>4980</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -3421,22 +3421,22 @@
         <v>7.23</v>
       </c>
       <c r="L9" t="n">
-        <v>38248.2</v>
+        <v>35526.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2478</v>
+        <v>1764</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1247.77</v>
+        <v>141413.95</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>17640</v>
       </c>
       <c r="H10" t="n">
-        <v>3240</v>
+        <v>3030</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,22 +3474,22 @@
         <v>2.61</v>
       </c>
       <c r="L10" t="n">
-        <v>39115.5</v>
+        <v>40717.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2550</v>
+        <v>969</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1296.38</v>
+        <v>146922.84</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>19590</v>
       </c>
       <c r="H11" t="n">
-        <v>4530</v>
+        <v>3930</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -3527,22 +3527,22 @@
         <v>3.59</v>
       </c>
       <c r="L11" t="n">
-        <v>57600</v>
+        <v>53730</v>
       </c>
       <c r="M11" t="n">
-        <v>1809</v>
+        <v>3186</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>127.5</v>
+        <v>51</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1222.16</v>
+        <v>138510.9</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>32550</v>
       </c>
       <c r="H12" t="n">
-        <v>4620</v>
+        <v>5220</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,22 +3580,22 @@
         <v>3.71</v>
       </c>
       <c r="L12" t="n">
-        <v>92250</v>
+        <v>95130</v>
       </c>
       <c r="M12" t="n">
-        <v>969</v>
+        <v>4161</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1805.41</v>
+        <v>204613.02</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>28320</v>
       </c>
       <c r="H13" t="n">
-        <v>1440</v>
+        <v>1860</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>4.75</v>
       </c>
       <c r="L13" t="n">
-        <v>68340</v>
+        <v>78570</v>
       </c>
       <c r="M13" t="n">
-        <v>300</v>
+        <v>3780</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1798.09</v>
+        <v>203783.76</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>15240</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -3686,10 +3686,10 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>32430</v>
+        <v>38820</v>
       </c>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>3720</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1001.02</v>
+        <v>113449.5</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>4350</v>
       </c>
       <c r="H15" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>13200</v>
+        <v>19170</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>388.42</v>
+        <v>44021.16</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>3060</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5910</v>
+        <v>12000</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>286.88</v>
+        <v>32512.5</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>570</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1800</v>
+        <v>4170</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>12692.88</v>
       </c>
     </row>
     <row r="18">
@@ -3886,7 +3886,7 @@
         <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>990</v>
+        <v>2100</v>
       </c>
       <c r="M18" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>54</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="19">
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19.36</v>
+        <v>2194.02</v>
       </c>
     </row>
     <row r="20">
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>600</v>
+        <v>2940</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.289999999999999</v>
+        <v>939.42</v>
       </c>
     </row>
     <row r="21">
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.59</v>
+        <v>180.54</v>
       </c>
     </row>
     <row r="22">
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.38</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="23">
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8372160</v>
+        <v>9849600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,13 +4501,13 @@
         <v>64288.14</v>
       </c>
       <c r="L5" t="n">
-        <v>808542</v>
+        <v>678132</v>
       </c>
       <c r="M5" t="n">
-        <v>57120</v>
+        <v>35070</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>1326</v>
       </c>
       <c r="O5" t="n">
         <v>255</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7341.03</v>
+        <v>831983.4</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>22356</v>
       </c>
       <c r="H6" t="n">
-        <v>9357120</v>
+        <v>11306520</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>1520478</v>
+        <v>1224774</v>
       </c>
       <c r="M6" t="n">
-        <v>278880</v>
+        <v>141120</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>2550</v>
+        <v>1275</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>265234.5</v>
+        <v>30059910</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>69984</v>
       </c>
       <c r="H7" t="n">
-        <v>15354090</v>
+        <v>13731300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>309787.28</v>
       </c>
       <c r="L7" t="n">
-        <v>3022920</v>
+        <v>2290680</v>
       </c>
       <c r="M7" t="n">
-        <v>944475</v>
+        <v>481425</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>51765</v>
+        <v>44625</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>467337.6</v>
+        <v>52964928</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>543348</v>
       </c>
       <c r="H8" t="n">
-        <v>18023400</v>
+        <v>14244300</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,10 +4660,10 @@
         <v>464583.81</v>
       </c>
       <c r="L8" t="n">
-        <v>4811670</v>
+        <v>4217400</v>
       </c>
       <c r="M8" t="n">
-        <v>1276275</v>
+        <v>462000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>716466.0600000001</v>
+        <v>81199486.8</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>918459</v>
       </c>
       <c r="H9" t="n">
-        <v>20007000</v>
+        <v>28386000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -4713,22 +4713,22 @@
         <v>350914.21</v>
       </c>
       <c r="L9" t="n">
-        <v>6884676</v>
+        <v>6394788</v>
       </c>
       <c r="M9" t="n">
-        <v>867300</v>
+        <v>617400</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16830</v>
+        <v>28050</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>748662.1</v>
+        <v>84848371.56</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>952560</v>
       </c>
       <c r="H10" t="n">
-        <v>18468000</v>
+        <v>17271000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,22 +4766,22 @@
         <v>126731.16</v>
       </c>
       <c r="L10" t="n">
-        <v>7040790</v>
+        <v>7329150</v>
       </c>
       <c r="M10" t="n">
-        <v>892500</v>
+        <v>339150</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14280</v>
+        <v>21420</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>777826.8</v>
+        <v>88153704</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>1057860</v>
       </c>
       <c r="H11" t="n">
-        <v>25821000</v>
+        <v>22401000</v>
       </c>
       <c r="I11" t="n">
         <v>349020.53</v>
@@ -4819,22 +4819,22 @@
         <v>174510.26</v>
       </c>
       <c r="L11" t="n">
-        <v>10368000</v>
+        <v>9671400</v>
       </c>
       <c r="M11" t="n">
-        <v>633150</v>
+        <v>1115100</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>21675</v>
+        <v>8670</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>733293</v>
+        <v>83106540</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1757700</v>
       </c>
       <c r="H12" t="n">
-        <v>26334000</v>
+        <v>29754000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,22 +4872,22 @@
         <v>180045.65</v>
       </c>
       <c r="L12" t="n">
-        <v>16605000</v>
+        <v>17123400</v>
       </c>
       <c r="M12" t="n">
-        <v>339150</v>
+        <v>1456350</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>25500</v>
+        <v>40800</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1083245.4</v>
+        <v>122767812</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>1529280</v>
       </c>
       <c r="H13" t="n">
-        <v>8208000</v>
+        <v>10602000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>230519.61</v>
       </c>
       <c r="L13" t="n">
-        <v>12301200</v>
+        <v>14142600</v>
       </c>
       <c r="M13" t="n">
-        <v>105000</v>
+        <v>1323000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1078855.2</v>
+        <v>122270256</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>822960</v>
       </c>
       <c r="H14" t="n">
-        <v>4275000</v>
+        <v>4446000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -4978,10 +4978,10 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>5837400</v>
+        <v>6987600</v>
       </c>
       <c r="M14" t="n">
-        <v>73500</v>
+        <v>1302000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>600615</v>
+        <v>68069700</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>234900</v>
       </c>
       <c r="H15" t="n">
-        <v>2052000</v>
+        <v>3078000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2376000</v>
+        <v>3450600</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>1239000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>233053.2</v>
+        <v>26412696</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>165240</v>
       </c>
       <c r="H16" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1063800</v>
+        <v>2160000</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>682500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>172125</v>
+        <v>19507500</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>30780</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>324000</v>
+        <v>750600</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>262500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>67197.60000000001</v>
+        <v>7615728</v>
       </c>
     </row>
     <row r="18">
@@ -5178,7 +5178,7 @@
         <v>6480</v>
       </c>
       <c r="H18" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>178200</v>
+        <v>378000</v>
       </c>
       <c r="M18" t="n">
-        <v>42000</v>
+        <v>325500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32400</v>
+        <v>3672000</v>
       </c>
     </row>
     <row r="19">
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>135000</v>
+        <v>270000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>399000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11615.4</v>
+        <v>1316412</v>
       </c>
     </row>
     <row r="20">
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>108000</v>
+        <v>529200</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>535500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4973.4</v>
+        <v>563652</v>
       </c>
     </row>
     <row r="21">
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>955.8</v>
+        <v>108324</v>
       </c>
     </row>
     <row r="22">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>226.8</v>
+        <v>25704</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>48270</v>
       </c>
       <c r="H4" t="n">
-        <v>6240</v>
+        <v>7860</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>144780</v>
+        <v>164190</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8070</v>
+        <v>7110</v>
       </c>
       <c r="O4" t="n">
-        <v>20280</v>
+        <v>21180</v>
       </c>
       <c r="P4" t="n">
-        <v>11460</v>
+        <v>7950</v>
       </c>
       <c r="Q4" t="n">
-        <v>26725.04</v>
+        <v>140658.12</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>17790</v>
       </c>
       <c r="H5" t="n">
-        <v>2190</v>
+        <v>3180</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>58530</v>
+        <v>76320</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>11490</v>
+        <v>12360</v>
       </c>
       <c r="O5" t="n">
-        <v>8910</v>
+        <v>13560</v>
       </c>
       <c r="P5" t="n">
-        <v>9150</v>
+        <v>11970</v>
       </c>
       <c r="Q5" t="n">
-        <v>11916.58</v>
+        <v>62718.84</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>2250</v>
       </c>
       <c r="H6" t="n">
-        <v>330</v>
+        <v>600</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11220</v>
+        <v>17160</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1260</v>
+        <v>2610</v>
       </c>
       <c r="O6" t="n">
-        <v>420</v>
+        <v>1290</v>
       </c>
       <c r="P6" t="n">
-        <v>6000</v>
+        <v>8790</v>
       </c>
       <c r="Q6" t="n">
-        <v>1302.4</v>
+        <v>6854.76</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>630</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3090</v>
+        <v>4890</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5610</v>
+        <v>8730</v>
       </c>
       <c r="Q7" t="n">
-        <v>104.04</v>
+        <v>547.5599999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1920</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5220</v>
+        <v>9960</v>
       </c>
       <c r="Q8" t="n">
-        <v>48.02</v>
+        <v>252.72</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4290</v>
+        <v>10080</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.42</v>
+        <v>128.52</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2010</v>
+        <v>5490</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.52</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>788.4</v>
+        <v>1144.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>12291.3</v>
+        <v>16027.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>114.9</v>
+        <v>123.6</v>
       </c>
       <c r="O5" t="n">
-        <v>445.5</v>
+        <v>678</v>
       </c>
       <c r="P5" t="n">
-        <v>183</v>
+        <v>239.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>595.83</v>
+        <v>3135.94</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>112.5</v>
       </c>
       <c r="H6" t="n">
-        <v>188.1</v>
+        <v>342</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4151.4</v>
+        <v>6349.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>63</v>
+        <v>130.5</v>
       </c>
       <c r="O6" t="n">
-        <v>105</v>
+        <v>322.5</v>
       </c>
       <c r="P6" t="n">
-        <v>900</v>
+        <v>1318.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>976.8</v>
+        <v>5141.07</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>94.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>175.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1854</v>
+        <v>2934</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1402.5</v>
+        <v>2182.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.23</v>
+        <v>438.05</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>1363.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1983.6</v>
+        <v>3784.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.62</v>
+        <v>240.08</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>145.8</v>
+        <v>826.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2145</v>
+        <v>5040</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.69</v>
+        <v>124.66</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>186.9</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1708.5</v>
+        <v>4666.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.52</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4493880</v>
+        <v>6525360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>2212434</v>
+        <v>2884896</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>19533</v>
+        <v>21012</v>
       </c>
       <c r="O5" t="n">
-        <v>75735</v>
+        <v>115260</v>
       </c>
       <c r="P5" t="n">
-        <v>11895</v>
+        <v>15561</v>
       </c>
       <c r="Q5" t="n">
-        <v>357497.39</v>
+        <v>1881565.2</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>6075</v>
       </c>
       <c r="H6" t="n">
-        <v>1072170</v>
+        <v>1949400</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>747252</v>
+        <v>1142856</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>10710</v>
+        <v>22185</v>
       </c>
       <c r="O6" t="n">
-        <v>17850</v>
+        <v>54825</v>
       </c>
       <c r="P6" t="n">
-        <v>58500</v>
+        <v>85702.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>586081.98</v>
+        <v>3084642</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>5103</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>998640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>333720</v>
+        <v>528120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>91162.5</v>
+        <v>141862.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>49937.47</v>
+        <v>262828.8</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>245376</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>128934</v>
+        <v>246012</v>
       </c>
       <c r="Q8" t="n">
-        <v>27369.58</v>
+        <v>144050.4</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26244</v>
+        <v>148716</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>139425</v>
+        <v>327600</v>
       </c>
       <c r="Q9" t="n">
-        <v>14211.74</v>
+        <v>74798.64</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>33642</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>111052.5</v>
+        <v>303322.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7510.32</v>
+        <v>39528</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>87030</v>
       </c>
       <c r="H4" t="n">
-        <v>5280</v>
+        <v>6210</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>138210</v>
+        <v>159360</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>22890</v>
+        <v>23490</v>
       </c>
       <c r="O4" t="n">
-        <v>32910</v>
+        <v>32940</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>33295.16</v>
+        <v>180671.4</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>25740</v>
       </c>
       <c r="H5" t="n">
-        <v>3810</v>
+        <v>4290</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>48660</v>
+        <v>56400</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8730</v>
+        <v>11580</v>
       </c>
       <c r="O5" t="n">
-        <v>28740</v>
+        <v>28050</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9409.209999999999</v>
+        <v>51057.72</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>7980</v>
       </c>
       <c r="H6" t="n">
-        <v>1440</v>
+        <v>1890</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>13890</v>
+        <v>21810</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4080</v>
+        <v>4650</v>
       </c>
       <c r="O6" t="n">
-        <v>25410</v>
+        <v>26370</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1532.64</v>
+        <v>8316.629999999999</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>2910</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3780</v>
+        <v>7740</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1650</v>
+        <v>3270</v>
       </c>
       <c r="O7" t="n">
-        <v>11970</v>
+        <v>15960</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>320.2</v>
+        <v>1737.54</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>780</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2040</v>
+        <v>3510</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>270</v>
+        <v>870</v>
       </c>
       <c r="O8" t="n">
-        <v>2790</v>
+        <v>5250</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>118.65</v>
+        <v>643.86</v>
       </c>
     </row>
     <row r="9">
@@ -9881,22 +9881,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O9" t="n">
-        <v>510</v>
+        <v>960</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.97</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1371.6</v>
+        <v>1544.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>3.31</v>
       </c>
       <c r="L5" t="n">
-        <v>10218.6</v>
+        <v>11844</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>87.3</v>
+        <v>115.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1437</v>
+        <v>1402.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>470.46</v>
+        <v>2552.89</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>399</v>
       </c>
       <c r="H6" t="n">
-        <v>820.8</v>
+        <v>1077.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5139.3</v>
+        <v>8069.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>204</v>
+        <v>232.5</v>
       </c>
       <c r="O6" t="n">
-        <v>6352.5</v>
+        <v>6592.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1149.48</v>
+        <v>6237.47</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>436.5</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>416.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2268</v>
+        <v>4644</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>115.5</v>
+        <v>228.9</v>
       </c>
       <c r="O7" t="n">
-        <v>4189.5</v>
+        <v>5586</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>256.16</v>
+        <v>1390.03</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>507</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1448.4</v>
+        <v>2492.1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="O8" t="n">
-        <v>1255.5</v>
+        <v>2362.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>112.72</v>
+        <v>611.67</v>
       </c>
     </row>
     <row r="9">
@@ -11173,22 +11173,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>280.5</v>
+        <v>528</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.76</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7818120</v>
+        <v>8803080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>160720.36</v>
       </c>
       <c r="L5" t="n">
-        <v>1839348</v>
+        <v>2131920</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14841</v>
+        <v>19686</v>
       </c>
       <c r="O5" t="n">
-        <v>244290</v>
+        <v>238425</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>282276.25</v>
+        <v>1531731.6</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>21546</v>
       </c>
       <c r="H6" t="n">
-        <v>4678560</v>
+        <v>6140610</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>925074</v>
+        <v>1452546</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>34680</v>
+        <v>39525</v>
       </c>
       <c r="O6" t="n">
-        <v>1079925</v>
+        <v>1120725</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>689686.24</v>
+        <v>3742483.5</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>23571</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>2371770</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>408240</v>
+        <v>835920</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>19635</v>
+        <v>38913</v>
       </c>
       <c r="O7" t="n">
-        <v>712215</v>
+        <v>949620</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>153697.82</v>
+        <v>834019.2</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>27378</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>260712</v>
+        <v>448578</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>9180</v>
+        <v>29580</v>
       </c>
       <c r="O8" t="n">
-        <v>213435</v>
+        <v>401625</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>67632.89</v>
+        <v>367000.2</v>
       </c>
     </row>
     <row r="9">
@@ -12465,22 +12465,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>17496</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O9" t="n">
-        <v>47685</v>
+        <v>89760</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4054.21</v>
+        <v>21999.6</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>84000</v>
       </c>
       <c r="H4" t="n">
-        <v>7080</v>
+        <v>8070</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>132</v>
       </c>
       <c r="L4" t="n">
-        <v>172410</v>
+        <v>176940</v>
       </c>
       <c r="M4" t="n">
-        <v>12720</v>
+        <v>150</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>34260</v>
+        <v>37650</v>
       </c>
       <c r="P4" t="n">
-        <v>17970</v>
+        <v>3360</v>
       </c>
       <c r="Q4" t="n">
         <v>35603.41</v>
@@ -13533,7 +13533,7 @@
         <v>68310</v>
       </c>
       <c r="H5" t="n">
-        <v>6270</v>
+        <v>6450</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -13545,19 +13545,19 @@
         <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>164760</v>
+        <v>154110</v>
       </c>
       <c r="M5" t="n">
-        <v>18540</v>
+        <v>1170</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31260</v>
+        <v>37680</v>
       </c>
       <c r="P5" t="n">
-        <v>29190</v>
+        <v>11220</v>
       </c>
       <c r="Q5" t="n">
         <v>29891.39</v>
@@ -13586,7 +13586,7 @@
         <v>70290</v>
       </c>
       <c r="H6" t="n">
-        <v>7710</v>
+        <v>7350</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>74</v>
       </c>
       <c r="L6" t="n">
-        <v>158640</v>
+        <v>139560</v>
       </c>
       <c r="M6" t="n">
-        <v>14430</v>
+        <v>2130</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>21240</v>
+        <v>21990</v>
       </c>
       <c r="P6" t="n">
-        <v>30570</v>
+        <v>17130</v>
       </c>
       <c r="Q6" t="n">
         <v>30989.2</v>
@@ -13639,7 +13639,7 @@
         <v>86460</v>
       </c>
       <c r="H7" t="n">
-        <v>11730</v>
+        <v>12420</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -13651,19 +13651,19 @@
         <v>74</v>
       </c>
       <c r="L7" t="n">
-        <v>202980</v>
+        <v>187590</v>
       </c>
       <c r="M7" t="n">
-        <v>9360</v>
+        <v>4530</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>20280</v>
+        <v>19770</v>
       </c>
       <c r="P7" t="n">
-        <v>33870</v>
+        <v>24120</v>
       </c>
       <c r="Q7" t="n">
         <v>41540.98</v>
@@ -13692,7 +13692,7 @@
         <v>58830</v>
       </c>
       <c r="H8" t="n">
-        <v>2610</v>
+        <v>3270</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -13704,19 +13704,19 @@
         <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>124680</v>
+        <v>121020</v>
       </c>
       <c r="M8" t="n">
-        <v>5790</v>
+        <v>6240</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>18660</v>
+        <v>18630</v>
       </c>
       <c r="P8" t="n">
-        <v>34890</v>
+        <v>30300</v>
       </c>
       <c r="Q8" t="n">
         <v>34379.38</v>
@@ -13745,7 +13745,7 @@
         <v>36240</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>73140</v>
+        <v>82890</v>
       </c>
       <c r="M9" t="n">
-        <v>3630</v>
+        <v>14220</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>27300</v>
+        <v>26580</v>
       </c>
       <c r="P9" t="n">
-        <v>32880</v>
+        <v>32190</v>
       </c>
       <c r="Q9" t="n">
         <v>29040.33</v>
@@ -13810,19 +13810,19 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>38430</v>
+        <v>45630</v>
       </c>
       <c r="M10" t="n">
-        <v>1740</v>
+        <v>9090</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>9750</v>
+        <v>14910</v>
       </c>
       <c r="P10" t="n">
-        <v>37050</v>
+        <v>40050</v>
       </c>
       <c r="Q10" t="n">
         <v>15561.84</v>
@@ -13863,19 +13863,19 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>9450</v>
+        <v>23970</v>
       </c>
       <c r="M11" t="n">
-        <v>630</v>
+        <v>10830</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>810</v>
+        <v>1860</v>
       </c>
       <c r="P11" t="n">
-        <v>32670</v>
+        <v>36690</v>
       </c>
       <c r="Q11" t="n">
         <v>1705.02</v>
@@ -13904,7 +13904,7 @@
         <v>930</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>34440</v>
       </c>
       <c r="M12" t="n">
-        <v>390</v>
+        <v>9660</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>30480</v>
+        <v>49470</v>
       </c>
       <c r="Q12" t="n">
         <v>353.1</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2880</v>
+        <v>19650</v>
       </c>
       <c r="M13" t="n">
-        <v>120</v>
+        <v>5370</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>23760</v>
+        <v>42270</v>
       </c>
       <c r="Q13" t="n">
         <v>222.64</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>5850</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>8610</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13290</v>
+        <v>22320</v>
       </c>
       <c r="Q14" t="n">
         <v>120.08</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>3510</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10950</v>
+        <v>11790</v>
       </c>
       <c r="Q15" t="n">
         <v>15.18</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>5730</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12600</v>
+        <v>21300</v>
       </c>
       <c r="Q16" t="n">
         <v>21.87</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2880</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10050</v>
+        <v>23370</v>
       </c>
       <c r="Q17" t="n">
         <v>12.72</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>2550</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3510</v>
+        <v>8010</v>
       </c>
       <c r="Q18" t="n">
         <v>5.91</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>1290</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q19" t="n">
         <v>1.79</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19537.2</v>
+        <v>21157.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.66</v>
@@ -14837,22 +14837,22 @@
         <v>85.40000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>187122.6</v>
+        <v>198009</v>
       </c>
       <c r="M5" t="n">
-        <v>1032</v>
+        <v>749.4</v>
       </c>
       <c r="N5" t="n">
-        <v>753.3</v>
+        <v>873.9</v>
       </c>
       <c r="O5" t="n">
-        <v>9108</v>
+        <v>10456.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1058.4</v>
+        <v>681.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>6878.18</v>
+        <v>71277.92999999999</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>11920.5</v>
       </c>
       <c r="H6" t="n">
-        <v>26026.2</v>
+        <v>26368.2</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>82.64</v>
       </c>
       <c r="L6" t="n">
-        <v>216039.3</v>
+        <v>216061.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2764.8</v>
+        <v>1850.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1290</v>
+        <v>1809</v>
       </c>
       <c r="O6" t="n">
-        <v>28567.5</v>
+        <v>30975</v>
       </c>
       <c r="P6" t="n">
-        <v>7753.5</v>
+        <v>5611.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>72134.42</v>
+        <v>747521.99</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>31554</v>
       </c>
       <c r="H7" t="n">
-        <v>31798.8</v>
+        <v>33375.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -14943,22 +14943,22 @@
         <v>98.89</v>
       </c>
       <c r="L7" t="n">
-        <v>323694</v>
+        <v>322182</v>
       </c>
       <c r="M7" t="n">
-        <v>8473.5</v>
+        <v>9303</v>
       </c>
       <c r="N7" t="n">
-        <v>640.5</v>
+        <v>987</v>
       </c>
       <c r="O7" t="n">
-        <v>29547</v>
+        <v>31857</v>
       </c>
       <c r="P7" t="n">
-        <v>15517.5</v>
+        <v>11310</v>
       </c>
       <c r="Q7" t="n">
-        <v>75062.52</v>
+        <v>777865.6</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>115927.5</v>
       </c>
       <c r="H8" t="n">
-        <v>22822.5</v>
+        <v>23944.5</v>
       </c>
       <c r="I8" t="n">
         <v>2.21</v>
@@ -14996,22 +14996,22 @@
         <v>75.06999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>314622.3</v>
+        <v>312449.7</v>
       </c>
       <c r="M8" t="n">
-        <v>10609.5</v>
+        <v>14404.5</v>
       </c>
       <c r="N8" t="n">
-        <v>330</v>
+        <v>792</v>
       </c>
       <c r="O8" t="n">
-        <v>27526.5</v>
+        <v>29376</v>
       </c>
       <c r="P8" t="n">
-        <v>26231.4</v>
+        <v>20987.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>75034.28</v>
+        <v>777572.95</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>137700</v>
       </c>
       <c r="H9" t="n">
-        <v>8040</v>
+        <v>10920</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -15049,22 +15049,22 @@
         <v>88.33</v>
       </c>
       <c r="L9" t="n">
-        <v>305694</v>
+        <v>319982.4</v>
       </c>
       <c r="M9" t="n">
-        <v>8148</v>
+        <v>24171</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>30393</v>
+        <v>35821.5</v>
       </c>
       <c r="P9" t="n">
-        <v>34110</v>
+        <v>31365</v>
       </c>
       <c r="Q9" t="n">
-        <v>73135.16</v>
+        <v>757892.58</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>133650</v>
       </c>
       <c r="H10" t="n">
-        <v>3750</v>
+        <v>3720</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>49.59</v>
       </c>
       <c r="L10" t="n">
-        <v>256747.2</v>
+        <v>285369.6</v>
       </c>
       <c r="M10" t="n">
-        <v>8721</v>
+        <v>20910</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>22491</v>
+        <v>31920</v>
       </c>
       <c r="P10" t="n">
-        <v>65662.5</v>
+        <v>65305.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>61107.36</v>
+        <v>633249.67</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>76320</v>
       </c>
       <c r="H11" t="n">
-        <v>4920</v>
+        <v>4590</v>
       </c>
       <c r="I11" t="n">
         <v>2.7</v>
@@ -15155,22 +15155,22 @@
         <v>31.45</v>
       </c>
       <c r="L11" t="n">
-        <v>181290</v>
+        <v>217320</v>
       </c>
       <c r="M11" t="n">
-        <v>5589</v>
+        <v>23463</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9256.5</v>
+        <v>18181.5</v>
       </c>
       <c r="P11" t="n">
-        <v>65772</v>
+        <v>82134</v>
       </c>
       <c r="Q11" t="n">
-        <v>38522.98</v>
+        <v>399209.92</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>59730</v>
       </c>
       <c r="H12" t="n">
-        <v>4680</v>
+        <v>5640</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>11.12</v>
       </c>
       <c r="L12" t="n">
-        <v>149370</v>
+        <v>198840</v>
       </c>
       <c r="M12" t="n">
-        <v>3334.5</v>
+        <v>21802.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4260</v>
+        <v>11940</v>
       </c>
       <c r="P12" t="n">
-        <v>58890</v>
+        <v>97800</v>
       </c>
       <c r="Q12" t="n">
-        <v>27256.85</v>
+        <v>282460.09</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>48270</v>
       </c>
       <c r="H13" t="n">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>96420</v>
+        <v>133470</v>
       </c>
       <c r="M13" t="n">
-        <v>2640</v>
+        <v>16440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2430</v>
+        <v>3870</v>
       </c>
       <c r="P13" t="n">
-        <v>42180</v>
+        <v>70350</v>
       </c>
       <c r="Q13" t="n">
-        <v>18676.15</v>
+        <v>193539.12</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>22260</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -15314,22 +15314,22 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>41490</v>
+        <v>57960</v>
       </c>
       <c r="M14" t="n">
-        <v>1170</v>
+        <v>16890</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3480</v>
+        <v>3150</v>
       </c>
       <c r="P14" t="n">
-        <v>28320</v>
+        <v>36720</v>
       </c>
       <c r="Q14" t="n">
-        <v>8832.25</v>
+        <v>91527.72</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>5520</v>
       </c>
       <c r="H15" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16230</v>
+        <v>30420</v>
       </c>
       <c r="M15" t="n">
-        <v>300</v>
+        <v>6090</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>780</v>
+        <v>1350</v>
       </c>
       <c r="P15" t="n">
-        <v>30150</v>
+        <v>33360</v>
       </c>
       <c r="Q15" t="n">
-        <v>3171.34</v>
+        <v>32864.26</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>3780</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7200</v>
+        <v>24150</v>
       </c>
       <c r="M16" t="n">
+        <v>3150</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>150</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>30</v>
-      </c>
       <c r="P16" t="n">
-        <v>38610</v>
+        <v>55590</v>
       </c>
       <c r="Q16" t="n">
-        <v>2198.63</v>
+        <v>22784.21</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>1290</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2310</v>
+        <v>9480</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>1590</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>21300</v>
+        <v>32790</v>
       </c>
       <c r="Q17" t="n">
-        <v>1136.31</v>
+        <v>11775.48</v>
       </c>
     </row>
     <row r="18">
@@ -15514,7 +15514,7 @@
         <v>330</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1560</v>
+        <v>6180</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>21180</v>
+        <v>30600</v>
       </c>
       <c r="Q18" t="n">
-        <v>537.02</v>
+        <v>5565.08</v>
       </c>
     </row>
     <row r="19">
@@ -15579,22 +15579,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1410</v>
+        <v>3810</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>1230</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>17820</v>
+        <v>30990</v>
       </c>
       <c r="Q19" t="n">
-        <v>250.43</v>
+        <v>2595.19</v>
       </c>
     </row>
     <row r="20">
@@ -15620,7 +15620,7 @@
         <v>3630</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>600</v>
+        <v>3150</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2010</v>
+        <v>5370</v>
       </c>
       <c r="Q20" t="n">
-        <v>74.44</v>
+        <v>771.39</v>
       </c>
     </row>
     <row r="21">
@@ -15697,10 +15697,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.73</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="22">
@@ -15738,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.67</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="23">
@@ -15791,7 +15791,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2257.2</v>
+        <v>2322</v>
       </c>
       <c r="I5" t="n">
         <v>1.32</v>
@@ -16129,19 +16129,19 @@
         <v>28.47</v>
       </c>
       <c r="L5" t="n">
-        <v>34599.6</v>
+        <v>32363.1</v>
       </c>
       <c r="M5" t="n">
-        <v>370.8</v>
+        <v>23.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1563</v>
+        <v>1884</v>
       </c>
       <c r="P5" t="n">
-        <v>583.8</v>
+        <v>224.4</v>
       </c>
       <c r="Q5" t="n">
         <v>1494.57</v>
@@ -16170,7 +16170,7 @@
         <v>3514.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4394.7</v>
+        <v>4189.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>37.52</v>
       </c>
       <c r="L6" t="n">
-        <v>58696.8</v>
+        <v>51637.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1154.4</v>
+        <v>170.4</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5310</v>
+        <v>5497.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4585.5</v>
+        <v>2569.5</v>
       </c>
       <c r="Q6" t="n">
         <v>23241.9</v>
@@ -16223,7 +16223,7 @@
         <v>12969</v>
       </c>
       <c r="H7" t="n">
-        <v>8562.9</v>
+        <v>9066.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -16235,19 +16235,19 @@
         <v>47.21</v>
       </c>
       <c r="L7" t="n">
-        <v>121788</v>
+        <v>112554</v>
       </c>
       <c r="M7" t="n">
-        <v>3276</v>
+        <v>1585.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7098</v>
+        <v>6919.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8467.5</v>
+        <v>6030</v>
       </c>
       <c r="Q7" t="n">
         <v>33232.78</v>
@@ -16276,7 +16276,7 @@
         <v>38239.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2218.5</v>
+        <v>2779.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -16288,19 +16288,19 @@
         <v>29.44</v>
       </c>
       <c r="L8" t="n">
-        <v>88522.8</v>
+        <v>85924.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3184.5</v>
+        <v>3432</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8397</v>
+        <v>8383.5</v>
       </c>
       <c r="P8" t="n">
-        <v>13258.2</v>
+        <v>11514</v>
       </c>
       <c r="Q8" t="n">
         <v>32660.42</v>
@@ -16329,7 +16329,7 @@
         <v>30804</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>27.3</v>
       </c>
       <c r="L9" t="n">
-        <v>59243.4</v>
+        <v>67140.89999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>2541</v>
+        <v>9954</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>15015</v>
+        <v>14619</v>
       </c>
       <c r="P9" t="n">
-        <v>16440</v>
+        <v>16095</v>
       </c>
       <c r="Q9" t="n">
         <v>28169.12</v>
@@ -16394,19 +16394,19 @@
         <v>4.35</v>
       </c>
       <c r="L10" t="n">
-        <v>34202.7</v>
+        <v>40610.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1479</v>
+        <v>7726.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6825</v>
+        <v>10437</v>
       </c>
       <c r="P10" t="n">
-        <v>31492.5</v>
+        <v>34042.5</v>
       </c>
       <c r="Q10" t="n">
         <v>15561.84</v>
@@ -16447,19 +16447,19 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>9450</v>
+        <v>23970</v>
       </c>
       <c r="M11" t="n">
-        <v>567</v>
+        <v>9747</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>688.5</v>
+        <v>1581</v>
       </c>
       <c r="P11" t="n">
-        <v>29403</v>
+        <v>33021</v>
       </c>
       <c r="Q11" t="n">
         <v>1705.02</v>
@@ -16488,7 +16488,7 @@
         <v>930</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>1.85</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>34440</v>
       </c>
       <c r="M12" t="n">
-        <v>370.5</v>
+        <v>9177</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>30480</v>
+        <v>49470</v>
       </c>
       <c r="Q12" t="n">
         <v>353.1</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2880</v>
+        <v>19650</v>
       </c>
       <c r="M13" t="n">
-        <v>120</v>
+        <v>5370</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>23760</v>
+        <v>42270</v>
       </c>
       <c r="Q13" t="n">
         <v>222.64</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>840</v>
+        <v>5850</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>8610</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13290</v>
+        <v>22320</v>
       </c>
       <c r="Q14" t="n">
         <v>120.08</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>3510</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10950</v>
+        <v>11790</v>
       </c>
       <c r="Q15" t="n">
         <v>15.18</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>5730</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12600</v>
+        <v>21300</v>
       </c>
       <c r="Q16" t="n">
         <v>21.87</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2880</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10050</v>
+        <v>23370</v>
       </c>
       <c r="Q17" t="n">
         <v>12.72</v>
@@ -16818,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>2550</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3510</v>
+        <v>8010</v>
       </c>
       <c r="Q18" t="n">
         <v>5.91</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>570</v>
+        <v>1290</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q19" t="n">
         <v>1.79</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>12866040</v>
+        <v>13235400</v>
       </c>
       <c r="I5" t="n">
         <v>257152.58</v>
@@ -17421,19 +17421,19 @@
         <v>1382195.1</v>
       </c>
       <c r="L5" t="n">
-        <v>6227928</v>
+        <v>5825358</v>
       </c>
       <c r="M5" t="n">
-        <v>129780</v>
+        <v>8190</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>265710</v>
+        <v>320280</v>
       </c>
       <c r="P5" t="n">
-        <v>37947</v>
+        <v>14586</v>
       </c>
       <c r="Q5" t="n">
         <v>896741.71</v>
@@ -17462,7 +17462,7 @@
         <v>189783</v>
       </c>
       <c r="H6" t="n">
-        <v>25049790</v>
+        <v>23880150</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>1821724.01</v>
       </c>
       <c r="L6" t="n">
-        <v>10565424</v>
+        <v>9294696</v>
       </c>
       <c r="M6" t="n">
-        <v>404040</v>
+        <v>59640</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>902700</v>
+        <v>934575</v>
       </c>
       <c r="P6" t="n">
-        <v>298057.5</v>
+        <v>167017.5</v>
       </c>
       <c r="Q6" t="n">
         <v>13945139.82</v>
@@ -17515,7 +17515,7 @@
         <v>700326</v>
       </c>
       <c r="H7" t="n">
-        <v>48808530</v>
+        <v>51679620</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -17527,19 +17527,19 @@
         <v>2292425.87</v>
       </c>
       <c r="L7" t="n">
-        <v>21921840</v>
+        <v>20259720</v>
       </c>
       <c r="M7" t="n">
-        <v>1146600</v>
+        <v>554925</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1206660</v>
+        <v>1176315</v>
       </c>
       <c r="P7" t="n">
-        <v>550387.5</v>
+        <v>391950</v>
       </c>
       <c r="Q7" t="n">
         <v>19939670.21</v>
@@ -17568,7 +17568,7 @@
         <v>2064933</v>
       </c>
       <c r="H8" t="n">
-        <v>12645450</v>
+        <v>15843150</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -17580,19 +17580,19 @@
         <v>1429488.64</v>
       </c>
       <c r="L8" t="n">
-        <v>15934104</v>
+        <v>15466356</v>
       </c>
       <c r="M8" t="n">
-        <v>1114575</v>
+        <v>1201200</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1427490</v>
+        <v>1425195</v>
       </c>
       <c r="P8" t="n">
-        <v>861783</v>
+        <v>748410</v>
       </c>
       <c r="Q8" t="n">
         <v>19596249.11</v>
@@ -17621,7 +17621,7 @@
         <v>1663416</v>
       </c>
       <c r="H9" t="n">
-        <v>1539000</v>
+        <v>2565000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
-        <v>10663812</v>
+        <v>12085362</v>
       </c>
       <c r="M9" t="n">
-        <v>889350</v>
+        <v>3483900</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2552550</v>
+        <v>2485230</v>
       </c>
       <c r="P9" t="n">
-        <v>1068600</v>
+        <v>1046175</v>
       </c>
       <c r="Q9" t="n">
         <v>16901471.36</v>
@@ -17686,19 +17686,19 @@
         <v>211218.6</v>
       </c>
       <c r="L10" t="n">
-        <v>6156486</v>
+        <v>7309926</v>
       </c>
       <c r="M10" t="n">
-        <v>517650</v>
+        <v>2704275</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1160250</v>
+        <v>1774290</v>
       </c>
       <c r="P10" t="n">
-        <v>2047012.5</v>
+        <v>2212762.5</v>
       </c>
       <c r="Q10" t="n">
         <v>9337103.279999999</v>
@@ -17739,19 +17739,19 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>1701000</v>
+        <v>4314600</v>
       </c>
       <c r="M11" t="n">
-        <v>198450</v>
+        <v>3411450</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>117045</v>
+        <v>268770</v>
       </c>
       <c r="P11" t="n">
-        <v>1911195</v>
+        <v>2146365</v>
       </c>
       <c r="Q11" t="n">
         <v>1023014.88</v>
@@ -17780,7 +17780,7 @@
         <v>50220</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>90022.82000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>804600</v>
+        <v>6199200</v>
       </c>
       <c r="M12" t="n">
-        <v>129675</v>
+        <v>3211950</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P12" t="n">
-        <v>1981200</v>
+        <v>3215550</v>
       </c>
       <c r="Q12" t="n">
         <v>211861.44</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>518400</v>
+        <v>3537000</v>
       </c>
       <c r="M13" t="n">
-        <v>42000</v>
+        <v>1879500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1544400</v>
+        <v>2747550</v>
       </c>
       <c r="Q13" t="n">
         <v>133585.2</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>151200</v>
+        <v>1053000</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>3013500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>863850</v>
+        <v>1450800</v>
       </c>
       <c r="Q14" t="n">
         <v>72048.96000000001</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>86400</v>
+        <v>631800</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>336000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>711750</v>
+        <v>766350</v>
       </c>
       <c r="Q15" t="n">
         <v>9106.559999999999</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>48600</v>
+        <v>1031400</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>819000</v>
+        <v>1384500</v>
       </c>
       <c r="Q16" t="n">
         <v>13124.16</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>70200</v>
+        <v>518400</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>653250</v>
+        <v>1519050</v>
       </c>
       <c r="Q17" t="n">
         <v>7633.44</v>
@@ -18110,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>64800</v>
+        <v>459000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>228150</v>
+        <v>520650</v>
       </c>
       <c r="Q18" t="n">
         <v>3548.88</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>102600</v>
+        <v>232200</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>44850</v>
+        <v>79950</v>
       </c>
       <c r="Q19" t="n">
         <v>1071.36</v>
@@ -18216,7 +18216,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>107340</v>
       </c>
       <c r="H4" t="n">
-        <v>13650</v>
+        <v>16080</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>48</v>
       </c>
       <c r="L4" t="n">
-        <v>345630</v>
+        <v>388770</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>17700</v>
+        <v>14280</v>
       </c>
       <c r="O4" t="n">
-        <v>55260</v>
+        <v>54900</v>
       </c>
       <c r="P4" t="n">
-        <v>7650</v>
+        <v>2970</v>
       </c>
       <c r="Q4" t="n">
-        <v>34209.65</v>
+        <v>391985.55</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>30540</v>
       </c>
       <c r="H5" t="n">
-        <v>2910</v>
+        <v>4830</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>111990</v>
+        <v>141390</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25440</v>
+        <v>30000</v>
       </c>
       <c r="O5" t="n">
-        <v>34680</v>
+        <v>47820</v>
       </c>
       <c r="P5" t="n">
-        <v>6570</v>
+        <v>8340</v>
       </c>
       <c r="Q5" t="n">
-        <v>11143.53</v>
+        <v>127686.24</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>4110</v>
       </c>
       <c r="H6" t="n">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>18780</v>
+        <v>30120</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5550</v>
+        <v>10080</v>
       </c>
       <c r="O6" t="n">
-        <v>7560</v>
+        <v>9930</v>
       </c>
       <c r="P6" t="n">
-        <v>3810</v>
+        <v>7950</v>
       </c>
       <c r="Q6" t="n">
-        <v>1096.76</v>
+        <v>12567.06</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>7800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>420</v>
+      </c>
+      <c r="O7" t="n">
         <v>3090</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>150</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1800</v>
-      </c>
       <c r="P7" t="n">
-        <v>3630</v>
+        <v>8790</v>
       </c>
       <c r="Q7" t="n">
-        <v>144.2</v>
+        <v>1652.31</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1140</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18881,13 +18881,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>390</v>
+        <v>840</v>
       </c>
       <c r="P8" t="n">
-        <v>1710</v>
+        <v>6000</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.84</v>
+        <v>135.63</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1047.6</v>
+        <v>1738.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>23517.9</v>
+        <v>29691.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>254.4</v>
+        <v>300</v>
       </c>
       <c r="O5" t="n">
-        <v>1734</v>
+        <v>2391</v>
       </c>
       <c r="P5" t="n">
-        <v>131.4</v>
+        <v>166.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.1799999999999</v>
+        <v>6384.31</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>205.5</v>
       </c>
       <c r="H6" t="n">
-        <v>188.1</v>
+        <v>256.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6948.6</v>
+        <v>11144.4</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>277.5</v>
+        <v>504</v>
       </c>
       <c r="O6" t="n">
-        <v>1890</v>
+        <v>2482.5</v>
       </c>
       <c r="P6" t="n">
-        <v>571.5</v>
+        <v>1192.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>822.5700000000001</v>
+        <v>9425.299999999999</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1854</v>
+        <v>4680</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10.5</v>
+        <v>29.4</v>
       </c>
       <c r="O7" t="n">
-        <v>630</v>
+        <v>1081.5</v>
       </c>
       <c r="P7" t="n">
-        <v>907.5</v>
+        <v>2197.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>115.36</v>
+        <v>1321.85</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>809.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20173,13 +20173,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>175.5</v>
+        <v>378</v>
       </c>
       <c r="P8" t="n">
-        <v>649.8</v>
+        <v>2280</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.24</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>160.2</v>
+        <v>133.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5971320</v>
+        <v>9911160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>4233222</v>
+        <v>5344542</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>43248</v>
+        <v>51000</v>
       </c>
       <c r="O5" t="n">
-        <v>294780</v>
+        <v>406470</v>
       </c>
       <c r="P5" t="n">
-        <v>8541</v>
+        <v>10842</v>
       </c>
       <c r="Q5" t="n">
-        <v>334305.79</v>
+        <v>3830587.2</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>11097</v>
       </c>
       <c r="H6" t="n">
-        <v>1072170</v>
+        <v>1462050</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1250748</v>
+        <v>2005992</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>47175</v>
+        <v>85680</v>
       </c>
       <c r="O6" t="n">
-        <v>321300</v>
+        <v>422025</v>
       </c>
       <c r="P6" t="n">
-        <v>37147.5</v>
+        <v>77512.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>493542.72</v>
+        <v>5655177</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>333720</v>
+        <v>842400</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1785</v>
+        <v>4998</v>
       </c>
       <c r="O7" t="n">
-        <v>107100</v>
+        <v>183855</v>
       </c>
       <c r="P7" t="n">
-        <v>58987.5</v>
+        <v>142837.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>69216.77</v>
+        <v>793108.8</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>145692</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21465,13 +21465,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>29835</v>
+        <v>64260</v>
       </c>
       <c r="P8" t="n">
-        <v>42237</v>
+        <v>148200</v>
       </c>
       <c r="Q8" t="n">
-        <v>6746.98</v>
+        <v>77309.10000000001</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28836</v>
+        <v>24030</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>111362040</v>
+        <v>120596040</v>
       </c>
       <c r="I5" t="n">
         <v>321440.72</v>
@@ -22589,22 +22589,22 @@
         <v>4146585.29</v>
       </c>
       <c r="L5" t="n">
-        <v>33682068</v>
+        <v>35641620</v>
       </c>
       <c r="M5" t="n">
-        <v>361200</v>
+        <v>262290</v>
       </c>
       <c r="N5" t="n">
-        <v>128061</v>
+        <v>148563</v>
       </c>
       <c r="O5" t="n">
-        <v>1548360</v>
+        <v>1777605</v>
       </c>
       <c r="P5" t="n">
-        <v>68796</v>
+        <v>44304</v>
       </c>
       <c r="Q5" t="n">
-        <v>4126908.85</v>
+        <v>42766757.06</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>643707</v>
       </c>
       <c r="H6" t="n">
-        <v>148349340</v>
+        <v>150298740</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>4012716.4</v>
       </c>
       <c r="L6" t="n">
-        <v>38887074</v>
+        <v>38891070</v>
       </c>
       <c r="M6" t="n">
-        <v>967680</v>
+        <v>647640</v>
       </c>
       <c r="N6" t="n">
-        <v>219300</v>
+        <v>307530</v>
       </c>
       <c r="O6" t="n">
-        <v>4856475</v>
+        <v>5265750</v>
       </c>
       <c r="P6" t="n">
-        <v>503977.5</v>
+        <v>364747.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>43280650.62</v>
+        <v>448513193.92</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1703916</v>
       </c>
       <c r="H7" t="n">
-        <v>181253160</v>
+        <v>190240920</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -22695,22 +22695,22 @@
         <v>4801702.84</v>
       </c>
       <c r="L7" t="n">
-        <v>58264920</v>
+        <v>57992760</v>
       </c>
       <c r="M7" t="n">
-        <v>2965725</v>
+        <v>3256050</v>
       </c>
       <c r="N7" t="n">
-        <v>108885</v>
+        <v>167790</v>
       </c>
       <c r="O7" t="n">
-        <v>5022990</v>
+        <v>5415690</v>
       </c>
       <c r="P7" t="n">
-        <v>1008637.5</v>
+        <v>735150</v>
       </c>
       <c r="Q7" t="n">
-        <v>45037510.27</v>
+        <v>466719360.48</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>6260085</v>
       </c>
       <c r="H8" t="n">
-        <v>130088250</v>
+        <v>136483650</v>
       </c>
       <c r="I8" t="n">
         <v>428846.59</v>
@@ -22748,22 +22748,22 @@
         <v>3645196.03</v>
       </c>
       <c r="L8" t="n">
-        <v>56632014</v>
+        <v>56240946</v>
       </c>
       <c r="M8" t="n">
-        <v>3713325</v>
+        <v>5041575</v>
       </c>
       <c r="N8" t="n">
-        <v>56100</v>
+        <v>134640</v>
       </c>
       <c r="O8" t="n">
-        <v>4679505</v>
+        <v>4993920</v>
       </c>
       <c r="P8" t="n">
-        <v>1705041</v>
+        <v>1364181</v>
       </c>
       <c r="Q8" t="n">
-        <v>45020566.04</v>
+        <v>466543769.08</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>7435800</v>
       </c>
       <c r="H9" t="n">
-        <v>45828000</v>
+        <v>62244000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -22801,22 +22801,22 @@
         <v>4288951.48</v>
       </c>
       <c r="L9" t="n">
-        <v>55024920</v>
+        <v>57596832</v>
       </c>
       <c r="M9" t="n">
-        <v>2851800</v>
+        <v>8459850</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O9" t="n">
-        <v>5166810</v>
+        <v>6089655</v>
       </c>
       <c r="P9" t="n">
-        <v>2217150</v>
+        <v>2038725</v>
       </c>
       <c r="Q9" t="n">
-        <v>43881095.67</v>
+        <v>454735547.88</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>7217100</v>
       </c>
       <c r="H10" t="n">
-        <v>21375000</v>
+        <v>21204000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>2407892.04</v>
       </c>
       <c r="L10" t="n">
-        <v>46214496</v>
+        <v>51366528</v>
       </c>
       <c r="M10" t="n">
-        <v>3052350</v>
+        <v>7318500</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3823470</v>
+        <v>5426400</v>
       </c>
       <c r="P10" t="n">
-        <v>4268062.5</v>
+        <v>4244857.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>36664416.72</v>
+        <v>379949802.3</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>4121280</v>
       </c>
       <c r="H11" t="n">
-        <v>28044000</v>
+        <v>26163000</v>
       </c>
       <c r="I11" t="n">
         <v>523530.79</v>
@@ -22907,22 +22907,22 @@
         <v>1526964.81</v>
       </c>
       <c r="L11" t="n">
-        <v>32632200</v>
+        <v>39117600</v>
       </c>
       <c r="M11" t="n">
-        <v>1956150</v>
+        <v>8212050</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1573605</v>
+        <v>3090855</v>
       </c>
       <c r="P11" t="n">
-        <v>4275180</v>
+        <v>5338710</v>
       </c>
       <c r="Q11" t="n">
-        <v>23113788.48</v>
+        <v>239525953.2</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>3225420</v>
       </c>
       <c r="H12" t="n">
-        <v>26676000</v>
+        <v>32148000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>540136.9399999999</v>
       </c>
       <c r="L12" t="n">
-        <v>26886600</v>
+        <v>35791200</v>
       </c>
       <c r="M12" t="n">
-        <v>1167075</v>
+        <v>7630875</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>724200</v>
+        <v>2029800</v>
       </c>
       <c r="P12" t="n">
-        <v>3827850</v>
+        <v>6357000</v>
       </c>
       <c r="Q12" t="n">
-        <v>16354109.52</v>
+        <v>169476054.3</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>2606580</v>
       </c>
       <c r="H13" t="n">
-        <v>8208000</v>
+        <v>10944000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>276623.53</v>
       </c>
       <c r="L13" t="n">
-        <v>17355600</v>
+        <v>24024600</v>
       </c>
       <c r="M13" t="n">
-        <v>924000</v>
+        <v>5754000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>413100</v>
+        <v>657900</v>
       </c>
       <c r="P13" t="n">
-        <v>2741700</v>
+        <v>4572750</v>
       </c>
       <c r="Q13" t="n">
-        <v>11205689.04</v>
+        <v>116123471.1</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>1202040</v>
       </c>
       <c r="H14" t="n">
-        <v>4275000</v>
+        <v>4446000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -23066,22 +23066,22 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>7468200</v>
+        <v>10432800</v>
       </c>
       <c r="M14" t="n">
-        <v>409500</v>
+        <v>5911500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>591600</v>
+        <v>535500</v>
       </c>
       <c r="P14" t="n">
-        <v>1840800</v>
+        <v>2386800</v>
       </c>
       <c r="Q14" t="n">
-        <v>5299348.32</v>
+        <v>54916633.8</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>298080</v>
       </c>
       <c r="H15" t="n">
-        <v>2052000</v>
+        <v>3078000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2921400</v>
+        <v>5475600</v>
       </c>
       <c r="M15" t="n">
-        <v>105000</v>
+        <v>2131500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>132600</v>
+        <v>229500</v>
       </c>
       <c r="P15" t="n">
-        <v>1959750</v>
+        <v>2168400</v>
       </c>
       <c r="Q15" t="n">
-        <v>1902802.32</v>
+        <v>19718556.3</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>204120</v>
       </c>
       <c r="H16" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1296000</v>
+        <v>4347000</v>
       </c>
       <c r="M16" t="n">
-        <v>52500</v>
+        <v>1102500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5100</v>
+        <v>25500</v>
       </c>
       <c r="P16" t="n">
-        <v>2509650</v>
+        <v>3613350</v>
       </c>
       <c r="Q16" t="n">
-        <v>1319178.96</v>
+        <v>13670523.9</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>69660</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>415800</v>
+        <v>1706400</v>
       </c>
       <c r="M17" t="n">
-        <v>52500</v>
+        <v>556500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>5100</v>
       </c>
       <c r="P17" t="n">
-        <v>1384500</v>
+        <v>2131350</v>
       </c>
       <c r="Q17" t="n">
-        <v>681786.72</v>
+        <v>7065289.8</v>
       </c>
     </row>
     <row r="18">
@@ -23266,7 +23266,7 @@
         <v>17820</v>
       </c>
       <c r="H18" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>280800</v>
+        <v>1112400</v>
       </c>
       <c r="M18" t="n">
-        <v>63000</v>
+        <v>357000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>5100</v>
       </c>
       <c r="P18" t="n">
-        <v>1376700</v>
+        <v>1989000</v>
       </c>
       <c r="Q18" t="n">
-        <v>322211.52</v>
+        <v>3339046.8</v>
       </c>
     </row>
     <row r="19">
@@ -23331,22 +23331,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>253800</v>
+        <v>685800</v>
       </c>
       <c r="M19" t="n">
-        <v>31500</v>
+        <v>430500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="P19" t="n">
-        <v>1158300</v>
+        <v>2014350</v>
       </c>
       <c r="Q19" t="n">
-        <v>150258.24</v>
+        <v>1557111.6</v>
       </c>
     </row>
     <row r="20">
@@ -23372,7 +23372,7 @@
         <v>196020</v>
       </c>
       <c r="H20" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>108000</v>
+        <v>567000</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>567000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>130650</v>
+        <v>349050</v>
       </c>
       <c r="Q20" t="n">
-        <v>44662.32</v>
+        <v>462831.3</v>
       </c>
     </row>
     <row r="21">
@@ -23449,10 +23449,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q21" t="n">
-        <v>8838.719999999999</v>
+        <v>91594.8</v>
       </c>
     </row>
     <row r="22">
@@ -23490,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1004.4</v>
+        <v>10408.5</v>
       </c>
     </row>
     <row r="23">
@@ -23543,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -23816,7 +23816,7 @@
         <v>50220</v>
       </c>
       <c r="H4" t="n">
-        <v>3150</v>
+        <v>2880</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>73</v>
       </c>
       <c r="L4" t="n">
-        <v>137520</v>
+        <v>120330</v>
       </c>
       <c r="M4" t="n">
-        <v>44250</v>
+        <v>45990</v>
       </c>
       <c r="N4" t="n">
-        <v>15570</v>
+        <v>13350</v>
       </c>
       <c r="O4" t="n">
-        <v>17430</v>
+        <v>19440</v>
       </c>
       <c r="P4" t="n">
-        <v>1980</v>
+        <v>780</v>
       </c>
       <c r="Q4" t="n">
-        <v>10675.7</v>
+        <v>104663.7</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>58860</v>
       </c>
       <c r="H5" t="n">
-        <v>9390</v>
+        <v>8070</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>68</v>
       </c>
       <c r="L5" t="n">
-        <v>165330</v>
+        <v>152880</v>
       </c>
       <c r="M5" t="n">
-        <v>17910</v>
+        <v>27510</v>
       </c>
       <c r="N5" t="n">
-        <v>21120</v>
+        <v>21720</v>
       </c>
       <c r="O5" t="n">
-        <v>20310</v>
+        <v>20400</v>
       </c>
       <c r="P5" t="n">
-        <v>3000</v>
+        <v>1050</v>
       </c>
       <c r="Q5" t="n">
-        <v>18447.21</v>
+        <v>180855</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>64530</v>
       </c>
       <c r="H6" t="n">
-        <v>12810</v>
+        <v>13050</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>54</v>
       </c>
       <c r="L6" t="n">
-        <v>172830</v>
+        <v>162000</v>
       </c>
       <c r="M6" t="n">
-        <v>6780</v>
+        <v>13380</v>
       </c>
       <c r="N6" t="n">
-        <v>12510</v>
+        <v>14430</v>
       </c>
       <c r="O6" t="n">
-        <v>18630</v>
+        <v>21330</v>
       </c>
       <c r="P6" t="n">
-        <v>3360</v>
+        <v>1200</v>
       </c>
       <c r="Q6" t="n">
-        <v>22199.63</v>
+        <v>217643.4</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>64230</v>
       </c>
       <c r="H7" t="n">
-        <v>13260</v>
+        <v>13380</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>58</v>
       </c>
       <c r="L7" t="n">
-        <v>184440</v>
+        <v>186810</v>
       </c>
       <c r="M7" t="n">
-        <v>4950</v>
+        <v>13980</v>
       </c>
       <c r="N7" t="n">
-        <v>6120</v>
+        <v>8340</v>
       </c>
       <c r="O7" t="n">
-        <v>21180</v>
+        <v>20550</v>
       </c>
       <c r="P7" t="n">
-        <v>3960</v>
+        <v>1890</v>
       </c>
       <c r="Q7" t="n">
-        <v>23254.32</v>
+        <v>227983.5</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>85980</v>
       </c>
       <c r="H8" t="n">
-        <v>19440</v>
+        <v>20100</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -24040,22 +24040,22 @@
         <v>48</v>
       </c>
       <c r="L8" t="n">
-        <v>239370</v>
+        <v>235440</v>
       </c>
       <c r="M8" t="n">
-        <v>5130</v>
+        <v>12180</v>
       </c>
       <c r="N8" t="n">
-        <v>1290</v>
+        <v>2340</v>
       </c>
       <c r="O8" t="n">
-        <v>23160</v>
+        <v>23880</v>
       </c>
       <c r="P8" t="n">
-        <v>6120</v>
+        <v>4200</v>
       </c>
       <c r="Q8" t="n">
-        <v>24288.08</v>
+        <v>238118.4</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>99330</v>
       </c>
       <c r="H9" t="n">
-        <v>3930</v>
+        <v>5130</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>66</v>
       </c>
       <c r="L9" t="n">
-        <v>239700</v>
+        <v>246810</v>
       </c>
       <c r="M9" t="n">
-        <v>4140</v>
+        <v>10740</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>19620</v>
+        <v>22170</v>
       </c>
       <c r="P9" t="n">
-        <v>9270</v>
+        <v>6030</v>
       </c>
       <c r="Q9" t="n">
-        <v>28640.77</v>
+        <v>280791.9</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>92760</v>
       </c>
       <c r="H10" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>49</v>
       </c>
       <c r="L10" t="n">
-        <v>198300</v>
+        <v>217320</v>
       </c>
       <c r="M10" t="n">
-        <v>5340</v>
+        <v>9390</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>20550</v>
+        <v>24570</v>
       </c>
       <c r="P10" t="n">
-        <v>12600</v>
+        <v>6450</v>
       </c>
       <c r="Q10" t="n">
-        <v>29775.79</v>
+        <v>291919.5</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>53640</v>
       </c>
       <c r="H11" t="n">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>112320</v>
+        <v>132150</v>
       </c>
       <c r="M11" t="n">
-        <v>3390</v>
+        <v>6450</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9900</v>
+        <v>18150</v>
       </c>
       <c r="P11" t="n">
-        <v>15930</v>
+        <v>9780</v>
       </c>
       <c r="Q11" t="n">
-        <v>23851.66</v>
+        <v>233839.8</v>
       </c>
     </row>
     <row r="12">
@@ -24240,7 +24240,7 @@
         <v>25800</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -24252,22 +24252,22 @@
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>51960</v>
+        <v>65250</v>
       </c>
       <c r="M12" t="n">
-        <v>2070</v>
+        <v>5400</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4200</v>
+        <v>11790</v>
       </c>
       <c r="P12" t="n">
-        <v>14190</v>
+        <v>15150</v>
       </c>
       <c r="Q12" t="n">
-        <v>14734.54</v>
+        <v>144456.3</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>25200</v>
+        <v>34170</v>
       </c>
       <c r="M13" t="n">
-        <v>2160</v>
+        <v>4710</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2430</v>
+        <v>3870</v>
       </c>
       <c r="P13" t="n">
-        <v>12300</v>
+        <v>12540</v>
       </c>
       <c r="Q13" t="n">
-        <v>8266.309999999999</v>
+        <v>81042.3</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7740</v>
+        <v>12510</v>
       </c>
       <c r="M14" t="n">
-        <v>810</v>
+        <v>4170</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3480</v>
+        <v>3150</v>
       </c>
       <c r="P14" t="n">
-        <v>12750</v>
+        <v>10650</v>
       </c>
       <c r="Q14" t="n">
-        <v>3177.84</v>
+        <v>31155.3</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2580</v>
+        <v>7800</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>1530</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>780</v>
+        <v>1350</v>
       </c>
       <c r="P15" t="n">
-        <v>18600</v>
+        <v>20490</v>
       </c>
       <c r="Q15" t="n">
-        <v>967.02</v>
+        <v>9480.6</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1020</v>
+        <v>6420</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="P16" t="n">
-        <v>26010</v>
+        <v>34290</v>
       </c>
       <c r="Q16" t="n">
-        <v>459.83</v>
+        <v>4508.1</v>
       </c>
     </row>
     <row r="17">
@@ -24517,10 +24517,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>120</v>
+        <v>2430</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>11250</v>
+        <v>9420</v>
       </c>
       <c r="Q17" t="n">
-        <v>178.46</v>
+        <v>1749.6</v>
       </c>
     </row>
     <row r="18">
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>210</v>
+        <v>1530</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>17700</v>
+        <v>22620</v>
       </c>
       <c r="Q18" t="n">
-        <v>117.23</v>
+        <v>1149.3</v>
       </c>
     </row>
     <row r="19">
@@ -24623,7 +24623,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>1020</v>
       </c>
       <c r="M19" t="n">
         <v>90</v>
@@ -24632,13 +24632,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>17130</v>
+        <v>29760</v>
       </c>
       <c r="Q19" t="n">
-        <v>100.98</v>
+        <v>990</v>
       </c>
     </row>
     <row r="20">
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2010</v>
+        <v>5370</v>
       </c>
       <c r="Q20" t="n">
-        <v>19.28</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
@@ -24741,10 +24741,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="22">
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3380.4</v>
+        <v>2905.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>22.51</v>
       </c>
       <c r="L5" t="n">
-        <v>34719.3</v>
+        <v>32104.8</v>
       </c>
       <c r="M5" t="n">
-        <v>358.2</v>
+        <v>550.2</v>
       </c>
       <c r="N5" t="n">
-        <v>211.2</v>
+        <v>217.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1015.5</v>
+        <v>1020</v>
       </c>
       <c r="P5" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="n">
-        <v>922.36</v>
+        <v>9042.75</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3226.5</v>
       </c>
       <c r="H6" t="n">
-        <v>7301.7</v>
+        <v>7438.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>27.38</v>
       </c>
       <c r="L6" t="n">
-        <v>63947.1</v>
+        <v>59940</v>
       </c>
       <c r="M6" t="n">
-        <v>542.4</v>
+        <v>1070.4</v>
       </c>
       <c r="N6" t="n">
-        <v>625.5</v>
+        <v>721.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4657.5</v>
+        <v>5332.5</v>
       </c>
       <c r="P6" t="n">
-        <v>504</v>
+        <v>180</v>
       </c>
       <c r="Q6" t="n">
-        <v>16649.72</v>
+        <v>163232.55</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>9634.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9679.799999999999</v>
+        <v>9767.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>110664</v>
+        <v>112086</v>
       </c>
       <c r="M7" t="n">
-        <v>1732.5</v>
+        <v>4893</v>
       </c>
       <c r="N7" t="n">
-        <v>428.4</v>
+        <v>583.8</v>
       </c>
       <c r="O7" t="n">
-        <v>7413</v>
+        <v>7192.5</v>
       </c>
       <c r="P7" t="n">
-        <v>990</v>
+        <v>472.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>18603.45</v>
+        <v>182386.8</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>55887</v>
       </c>
       <c r="H8" t="n">
-        <v>16524</v>
+        <v>17085</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -25332,22 +25332,22 @@
         <v>35.33</v>
       </c>
       <c r="L8" t="n">
-        <v>169952.7</v>
+        <v>167162.4</v>
       </c>
       <c r="M8" t="n">
-        <v>2821.5</v>
+        <v>6699</v>
       </c>
       <c r="N8" t="n">
-        <v>258</v>
+        <v>468</v>
       </c>
       <c r="O8" t="n">
-        <v>10422</v>
+        <v>10746</v>
       </c>
       <c r="P8" t="n">
-        <v>2325.6</v>
+        <v>1596</v>
       </c>
       <c r="Q8" t="n">
-        <v>23073.67</v>
+        <v>226212.48</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>84430.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3930</v>
+        <v>5130</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>194157</v>
+        <v>199916.1</v>
       </c>
       <c r="M9" t="n">
-        <v>2898</v>
+        <v>7518</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>10791</v>
+        <v>12193.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4635</v>
+        <v>3015</v>
       </c>
       <c r="Q9" t="n">
-        <v>27781.55</v>
+        <v>272368.14</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>92760</v>
       </c>
       <c r="H10" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>42.63</v>
       </c>
       <c r="L10" t="n">
-        <v>176487</v>
+        <v>193414.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4539</v>
+        <v>7981.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14385</v>
+        <v>17199</v>
       </c>
       <c r="P10" t="n">
-        <v>10710</v>
+        <v>5482.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>29775.79</v>
+        <v>291919.5</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>53640</v>
       </c>
       <c r="H11" t="n">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>26.06</v>
       </c>
       <c r="L11" t="n">
-        <v>112320</v>
+        <v>132150</v>
       </c>
       <c r="M11" t="n">
-        <v>3051</v>
+        <v>5805</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8415</v>
+        <v>15427.5</v>
       </c>
       <c r="P11" t="n">
-        <v>14337</v>
+        <v>8802</v>
       </c>
       <c r="Q11" t="n">
-        <v>23851.66</v>
+        <v>233839.8</v>
       </c>
     </row>
     <row r="12">
@@ -25532,7 +25532,7 @@
         <v>25800</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -25544,22 +25544,22 @@
         <v>5.56</v>
       </c>
       <c r="L12" t="n">
-        <v>51960</v>
+        <v>65250</v>
       </c>
       <c r="M12" t="n">
-        <v>1966.5</v>
+        <v>5130</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4200</v>
+        <v>11790</v>
       </c>
       <c r="P12" t="n">
-        <v>14190</v>
+        <v>15150</v>
       </c>
       <c r="Q12" t="n">
-        <v>14734.54</v>
+        <v>144456.3</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>25200</v>
+        <v>34170</v>
       </c>
       <c r="M13" t="n">
-        <v>2160</v>
+        <v>4710</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2430</v>
+        <v>3870</v>
       </c>
       <c r="P13" t="n">
-        <v>12300</v>
+        <v>12540</v>
       </c>
       <c r="Q13" t="n">
-        <v>8266.309999999999</v>
+        <v>81042.3</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7740</v>
+        <v>12510</v>
       </c>
       <c r="M14" t="n">
-        <v>810</v>
+        <v>4170</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3480</v>
+        <v>3150</v>
       </c>
       <c r="P14" t="n">
-        <v>12750</v>
+        <v>10650</v>
       </c>
       <c r="Q14" t="n">
-        <v>3177.84</v>
+        <v>31155.3</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2580</v>
+        <v>7800</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>1530</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>780</v>
+        <v>1350</v>
       </c>
       <c r="P15" t="n">
-        <v>18600</v>
+        <v>20490</v>
       </c>
       <c r="Q15" t="n">
-        <v>967.02</v>
+        <v>9480.6</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1020</v>
+        <v>6420</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="P16" t="n">
-        <v>26010</v>
+        <v>34290</v>
       </c>
       <c r="Q16" t="n">
-        <v>459.83</v>
+        <v>4508.1</v>
       </c>
     </row>
     <row r="17">
@@ -25809,10 +25809,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>120</v>
+        <v>2430</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>11250</v>
+        <v>9420</v>
       </c>
       <c r="Q17" t="n">
-        <v>178.46</v>
+        <v>1749.6</v>
       </c>
     </row>
     <row r="18">
@@ -25862,10 +25862,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>210</v>
+        <v>1530</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>17700</v>
+        <v>22620</v>
       </c>
       <c r="Q18" t="n">
-        <v>117.23</v>
+        <v>1149.3</v>
       </c>
     </row>
     <row r="19">
@@ -25915,7 +25915,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>1020</v>
       </c>
       <c r="M19" t="n">
         <v>90</v>
@@ -25924,13 +25924,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>17130</v>
+        <v>29760</v>
       </c>
       <c r="Q19" t="n">
-        <v>100.98</v>
+        <v>990</v>
       </c>
     </row>
     <row r="20">
@@ -25971,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2010</v>
+        <v>5370</v>
       </c>
       <c r="Q20" t="n">
-        <v>19.28</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="22">
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19268280</v>
+        <v>16559640</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>1092898.45</v>
       </c>
       <c r="L5" t="n">
-        <v>6249474</v>
+        <v>5778864</v>
       </c>
       <c r="M5" t="n">
-        <v>125370</v>
+        <v>192570</v>
       </c>
       <c r="N5" t="n">
-        <v>35904</v>
+        <v>36924</v>
       </c>
       <c r="O5" t="n">
-        <v>172635</v>
+        <v>173400</v>
       </c>
       <c r="P5" t="n">
-        <v>3900</v>
+        <v>1365</v>
       </c>
       <c r="Q5" t="n">
-        <v>553416.3</v>
+        <v>5425650</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>174231</v>
       </c>
       <c r="H6" t="n">
-        <v>41619690</v>
+        <v>42399450</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1329366.17</v>
       </c>
       <c r="L6" t="n">
-        <v>11510478</v>
+        <v>10789200</v>
       </c>
       <c r="M6" t="n">
-        <v>189840</v>
+        <v>374640</v>
       </c>
       <c r="N6" t="n">
-        <v>106335</v>
+        <v>122655</v>
       </c>
       <c r="O6" t="n">
-        <v>791775</v>
+        <v>906525</v>
       </c>
       <c r="P6" t="n">
-        <v>32760</v>
+        <v>11700</v>
       </c>
       <c r="Q6" t="n">
-        <v>9989832.060000001</v>
+        <v>97939530</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>520263</v>
       </c>
       <c r="H7" t="n">
-        <v>55174860</v>
+        <v>55674180</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1796766.22</v>
       </c>
       <c r="L7" t="n">
-        <v>19919520</v>
+        <v>20175480</v>
       </c>
       <c r="M7" t="n">
-        <v>606375</v>
+        <v>1712550</v>
       </c>
       <c r="N7" t="n">
-        <v>72828</v>
+        <v>99246</v>
       </c>
       <c r="O7" t="n">
-        <v>1260210</v>
+        <v>1222725</v>
       </c>
       <c r="P7" t="n">
-        <v>64350</v>
+        <v>30712.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>11162072.16</v>
+        <v>109432080</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>3017898</v>
       </c>
       <c r="H8" t="n">
-        <v>94186800</v>
+        <v>97384500</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -26624,22 +26624,22 @@
         <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
-        <v>30591486</v>
+        <v>30089232</v>
       </c>
       <c r="M8" t="n">
-        <v>987525</v>
+        <v>2344650</v>
       </c>
       <c r="N8" t="n">
-        <v>43860</v>
+        <v>79560</v>
       </c>
       <c r="O8" t="n">
-        <v>1771740</v>
+        <v>1826820</v>
       </c>
       <c r="P8" t="n">
-        <v>151164</v>
+        <v>103740</v>
       </c>
       <c r="Q8" t="n">
-        <v>13844203.78</v>
+        <v>135727488</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4559247</v>
       </c>
       <c r="H9" t="n">
-        <v>22401000</v>
+        <v>29241000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>2573370.89</v>
       </c>
       <c r="L9" t="n">
-        <v>34948260</v>
+        <v>35984898</v>
       </c>
       <c r="M9" t="n">
-        <v>1014300</v>
+        <v>2631300</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1834470</v>
+        <v>2072895</v>
       </c>
       <c r="P9" t="n">
-        <v>301275</v>
+        <v>195975</v>
       </c>
       <c r="Q9" t="n">
-        <v>16668930.35</v>
+        <v>163420885.8</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>5009040</v>
       </c>
       <c r="H10" t="n">
-        <v>2565000</v>
+        <v>3420000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>2069942.28</v>
       </c>
       <c r="L10" t="n">
-        <v>31767660</v>
+        <v>34814664</v>
       </c>
       <c r="M10" t="n">
-        <v>1588650</v>
+        <v>2793525</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2445450</v>
+        <v>2923830</v>
       </c>
       <c r="P10" t="n">
-        <v>696150</v>
+        <v>356362.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>17865473.4</v>
+        <v>175151700</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>2896560</v>
       </c>
       <c r="H11" t="n">
-        <v>1881000</v>
+        <v>2394000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>1265199.41</v>
       </c>
       <c r="L11" t="n">
-        <v>20217600</v>
+        <v>23787000</v>
       </c>
       <c r="M11" t="n">
-        <v>1067850</v>
+        <v>2031750</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1430550</v>
+        <v>2622675</v>
       </c>
       <c r="P11" t="n">
-        <v>931905</v>
+        <v>572130</v>
       </c>
       <c r="Q11" t="n">
-        <v>14310995.76</v>
+        <v>140303880</v>
       </c>
     </row>
     <row r="12">
@@ -26824,7 +26824,7 @@
         <v>1393200</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -26836,22 +26836,22 @@
         <v>270068.47</v>
       </c>
       <c r="L12" t="n">
-        <v>9352800</v>
+        <v>11745000</v>
       </c>
       <c r="M12" t="n">
-        <v>688275</v>
+        <v>1795500</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>714000</v>
+        <v>2004300</v>
       </c>
       <c r="P12" t="n">
-        <v>922350</v>
+        <v>984750</v>
       </c>
       <c r="Q12" t="n">
-        <v>8840725.560000001</v>
+        <v>86673780</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>4536000</v>
+        <v>6150600</v>
       </c>
       <c r="M13" t="n">
-        <v>756000</v>
+        <v>1648500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>413100</v>
+        <v>657900</v>
       </c>
       <c r="P13" t="n">
-        <v>799500</v>
+        <v>815100</v>
       </c>
       <c r="Q13" t="n">
-        <v>4959788.76</v>
+        <v>48625380</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1393200</v>
+        <v>2251800</v>
       </c>
       <c r="M14" t="n">
-        <v>283500</v>
+        <v>1459500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>591600</v>
+        <v>535500</v>
       </c>
       <c r="P14" t="n">
-        <v>828750</v>
+        <v>692250</v>
       </c>
       <c r="Q14" t="n">
-        <v>1906704.36</v>
+        <v>18693180</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>464400</v>
+        <v>1404000</v>
       </c>
       <c r="M15" t="n">
-        <v>31500</v>
+        <v>535500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>132600</v>
+        <v>229500</v>
       </c>
       <c r="P15" t="n">
-        <v>1209000</v>
+        <v>1331850</v>
       </c>
       <c r="Q15" t="n">
-        <v>580212.72</v>
+        <v>5688360</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>183600</v>
+        <v>1155600</v>
       </c>
       <c r="M16" t="n">
-        <v>31500</v>
+        <v>283500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5100</v>
+        <v>25500</v>
       </c>
       <c r="P16" t="n">
-        <v>1690650</v>
+        <v>2228850</v>
       </c>
       <c r="Q16" t="n">
-        <v>275895.72</v>
+        <v>2704860</v>
       </c>
     </row>
     <row r="17">
@@ -27101,10 +27101,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>21600</v>
+        <v>437400</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>262500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>5100</v>
       </c>
       <c r="P17" t="n">
-        <v>731250</v>
+        <v>612300</v>
       </c>
       <c r="Q17" t="n">
-        <v>107075.52</v>
+        <v>1049760</v>
       </c>
     </row>
     <row r="18">
@@ -27154,10 +27154,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>37800</v>
+        <v>275400</v>
       </c>
       <c r="M18" t="n">
-        <v>21000</v>
+        <v>31500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>5100</v>
       </c>
       <c r="P18" t="n">
-        <v>1150500</v>
+        <v>1470300</v>
       </c>
       <c r="Q18" t="n">
-        <v>70337.16</v>
+        <v>689580</v>
       </c>
     </row>
     <row r="19">
@@ -27207,7 +27207,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>16200</v>
+        <v>183600</v>
       </c>
       <c r="M19" t="n">
         <v>31500</v>
@@ -27216,13 +27216,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="P19" t="n">
-        <v>1113450</v>
+        <v>1934400</v>
       </c>
       <c r="Q19" t="n">
-        <v>60588</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="20">
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>130650</v>
+        <v>349050</v>
       </c>
       <c r="Q20" t="n">
-        <v>11566.8</v>
+        <v>113400</v>
       </c>
     </row>
     <row r="21">
@@ -27325,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q21" t="n">
-        <v>4020.84</v>
+        <v>39420</v>
       </c>
     </row>
     <row r="22">
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>55.08</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23">
@@ -27692,7 +27692,7 @@
         <v>133560</v>
       </c>
       <c r="H4" t="n">
-        <v>17580</v>
+        <v>18060</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>97</v>
       </c>
       <c r="L4" t="n">
-        <v>406980</v>
+        <v>434310</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>61110</v>
+        <v>57150</v>
       </c>
       <c r="P4" t="n">
-        <v>660</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>43928.07</v>
+        <v>611656.65</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>110550</v>
       </c>
       <c r="H5" t="n">
-        <v>22560</v>
+        <v>23790</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>260910</v>
+        <v>283500</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>54360</v>
+        <v>58500</v>
       </c>
       <c r="P5" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27914.64</v>
+        <v>388684.89</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>56370</v>
       </c>
       <c r="H6" t="n">
-        <v>18240</v>
+        <v>17520</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>135180</v>
+        <v>141840</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34860</v>
+        <v>35730</v>
       </c>
       <c r="P6" t="n">
-        <v>1710</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>13893.01</v>
+        <v>193446.99</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>31410</v>
       </c>
       <c r="H7" t="n">
-        <v>13350</v>
+        <v>14190</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>79080</v>
+        <v>83160</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>25410</v>
+        <v>28200</v>
       </c>
       <c r="P7" t="n">
-        <v>2610</v>
+        <v>60</v>
       </c>
       <c r="Q7" t="n">
-        <v>6883.33</v>
+        <v>95843.88</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>10860</v>
       </c>
       <c r="H8" t="n">
-        <v>1080</v>
+        <v>1830</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>21900</v>
+        <v>25170</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>9990</v>
+        <v>11310</v>
       </c>
       <c r="P8" t="n">
-        <v>4350</v>
+        <v>630</v>
       </c>
       <c r="Q8" t="n">
-        <v>1569.39</v>
+        <v>21852.27</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>330</v>
       </c>
       <c r="H9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4020</v>
+        <v>5610</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4470</v>
+        <v>10290</v>
       </c>
       <c r="P9" t="n">
-        <v>4380</v>
+        <v>1830</v>
       </c>
       <c r="Q9" t="n">
-        <v>100.96</v>
+        <v>1405.8</v>
       </c>
     </row>
     <row r="10">
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>690</v>
+        <v>1980</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1320</v>
+        <v>5460</v>
       </c>
       <c r="P10" t="n">
-        <v>5820</v>
+        <v>6480</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.8</v>
+        <v>373.23</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>90</v>
+        <v>1380</v>
       </c>
       <c r="P11" t="n">
-        <v>4200</v>
+        <v>8160</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.23</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2370</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="13">
@@ -28169,7 +28169,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1050</v>
+        <v>3870</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,10 +28246,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8121.6</v>
+        <v>8564.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -29049,7 +29049,7 @@
         <v>19.86</v>
       </c>
       <c r="L5" t="n">
-        <v>54791.1</v>
+        <v>59535</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2718</v>
+        <v>2925</v>
       </c>
       <c r="P5" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1395.73</v>
+        <v>19434.24</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2818.5</v>
       </c>
       <c r="H6" t="n">
-        <v>10396.8</v>
+        <v>9986.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>13.69</v>
       </c>
       <c r="L6" t="n">
-        <v>50016.6</v>
+        <v>52480.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8715</v>
+        <v>8932.5</v>
       </c>
       <c r="P6" t="n">
-        <v>256.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>10419.76</v>
+        <v>145085.24</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>4711.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9745.5</v>
+        <v>10358.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>7.66</v>
       </c>
       <c r="L7" t="n">
-        <v>47448</v>
+        <v>49896</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8893.5</v>
+        <v>9870</v>
       </c>
       <c r="P7" t="n">
-        <v>652.5</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>5506.67</v>
+        <v>76675.10000000001</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>7059</v>
       </c>
       <c r="H8" t="n">
-        <v>918</v>
+        <v>1555.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>15549</v>
+        <v>17870.7</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4495.5</v>
+        <v>5089.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1653</v>
+        <v>239.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1490.92</v>
+        <v>20759.66</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>280.5</v>
       </c>
       <c r="H9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3256.2</v>
+        <v>4544.1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2458.5</v>
+        <v>5659.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2190</v>
+        <v>915</v>
       </c>
       <c r="Q9" t="n">
-        <v>97.93000000000001</v>
+        <v>1363.63</v>
       </c>
     </row>
     <row r="10">
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>614.1</v>
+        <v>1762.2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>924</v>
+        <v>3822</v>
       </c>
       <c r="P10" t="n">
-        <v>4947</v>
+        <v>5508</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.8</v>
+        <v>373.23</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>76.5</v>
+        <v>1173</v>
       </c>
       <c r="P11" t="n">
-        <v>3780</v>
+        <v>7344</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.23</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2370</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="13">
@@ -29461,7 +29461,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1050</v>
+        <v>3870</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,10 +29538,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>46293120</v>
+        <v>48817080</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -30341,7 +30341,7 @@
         <v>964322.16</v>
       </c>
       <c r="L5" t="n">
-        <v>9862398</v>
+        <v>10716300</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>462060</v>
+        <v>497250</v>
       </c>
       <c r="P5" t="n">
-        <v>663</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>837439.26</v>
+        <v>11660546.7</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>152199</v>
       </c>
       <c r="H6" t="n">
-        <v>59261760</v>
+        <v>56922480</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>664683.08</v>
       </c>
       <c r="L6" t="n">
-        <v>9002988</v>
+        <v>9446544</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1481550</v>
+        <v>1518525</v>
       </c>
       <c r="P6" t="n">
-        <v>16672.5</v>
+        <v>292.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6251855</v>
+        <v>87051145.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>254421</v>
       </c>
       <c r="H7" t="n">
-        <v>55549350</v>
+        <v>59044590</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>371744.74</v>
       </c>
       <c r="L7" t="n">
-        <v>8540640</v>
+        <v>8981280</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1511895</v>
+        <v>1677900</v>
       </c>
       <c r="P7" t="n">
-        <v>42412.5</v>
+        <v>975</v>
       </c>
       <c r="Q7" t="n">
-        <v>3303999.94</v>
+        <v>46005062.4</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>381186</v>
       </c>
       <c r="H8" t="n">
-        <v>5232600</v>
+        <v>8866350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>2798820</v>
+        <v>3216726</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>764235</v>
+        <v>865215</v>
       </c>
       <c r="P8" t="n">
-        <v>107445</v>
+        <v>15561</v>
       </c>
       <c r="Q8" t="n">
-        <v>894552.47</v>
+        <v>12455793.9</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>15147</v>
       </c>
       <c r="H9" t="n">
-        <v>1881000</v>
+        <v>2052000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>586116</v>
+        <v>817938</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>417945</v>
+        <v>962115</v>
       </c>
       <c r="P9" t="n">
-        <v>142350</v>
+        <v>59475</v>
       </c>
       <c r="Q9" t="n">
-        <v>58759.88</v>
+        <v>818175.6</v>
       </c>
     </row>
     <row r="10">
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>110538</v>
+        <v>317196</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>157080</v>
+        <v>649740</v>
       </c>
       <c r="P10" t="n">
-        <v>321555</v>
+        <v>358020</v>
       </c>
       <c r="Q10" t="n">
-        <v>16082.82</v>
+        <v>223938</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>75600</v>
+        <v>437400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13005</v>
+        <v>199410</v>
       </c>
       <c r="P11" t="n">
-        <v>245700</v>
+        <v>477360</v>
       </c>
       <c r="Q11" t="n">
-        <v>6740.28</v>
+        <v>93852</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>1368000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5400</v>
+        <v>205200</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>154050</v>
+        <v>405600</v>
       </c>
       <c r="Q12" t="n">
-        <v>1322.46</v>
+        <v>18414</v>
       </c>
     </row>
     <row r="13">
@@ -30753,7 +30753,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>151200</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>68250</v>
+        <v>251550</v>
       </c>
       <c r="Q13" t="n">
-        <v>213.3</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9750</v>
+        <v>54600</v>
       </c>
       <c r="Q14" t="n">
-        <v>42.66</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15">
